--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380B8496-4D93-4367-A35F-6AF3EB1A74C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7387449E-FEC1-4802-8131-B7B5E005A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="WM" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AA!$A$1:$O$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AA!$A$1:$O$211</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WM!$A$1:$R$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="810">
   <si>
     <t>SKU</t>
   </si>
@@ -485,9 +485,6 @@
     <t>FBAM75673</t>
   </si>
   <si>
-    <t>FBA80006</t>
-  </si>
-  <si>
     <t>FBA79444</t>
   </si>
   <si>
@@ -650,15 +647,6 @@
     <t>FBA76717</t>
   </si>
   <si>
-    <t>FBA76731</t>
-  </si>
-  <si>
-    <t>FBA76713</t>
-  </si>
-  <si>
-    <t>FBA76709</t>
-  </si>
-  <si>
     <t>FBA76736</t>
   </si>
   <si>
@@ -680,18 +668,6 @@
     <t>FBA76740</t>
   </si>
   <si>
-    <t>FBA76710</t>
-  </si>
-  <si>
-    <t>FBA76711</t>
-  </si>
-  <si>
-    <t>FBA76712</t>
-  </si>
-  <si>
-    <t>FBA76714</t>
-  </si>
-  <si>
     <t>FBA78970</t>
   </si>
   <si>
@@ -701,24 +677,6 @@
     <t>FBA78978</t>
   </si>
   <si>
-    <t>FBA79006</t>
-  </si>
-  <si>
-    <t>FBA79007</t>
-  </si>
-  <si>
-    <t>FBA79326</t>
-  </si>
-  <si>
-    <t>FBA79327</t>
-  </si>
-  <si>
-    <t>FBA79328</t>
-  </si>
-  <si>
-    <t>FBA79329</t>
-  </si>
-  <si>
     <t>FBA79389</t>
   </si>
   <si>
@@ -1253,15 +1211,6 @@
     <t>B0BLK6P24G</t>
   </si>
   <si>
-    <t>B0BLK9QL7X</t>
-  </si>
-  <si>
-    <t>B0BLK1Z7PJ</t>
-  </si>
-  <si>
-    <t>B0BLJYX15C</t>
-  </si>
-  <si>
     <t>B0BLS63XCL</t>
   </si>
   <si>
@@ -1292,18 +1241,6 @@
     <t>B0CF5PCL34</t>
   </si>
   <si>
-    <t>B0CYLXLBRL</t>
-  </si>
-  <si>
-    <t>B0CYLVB618</t>
-  </si>
-  <si>
-    <t>B0CYLXL5GY</t>
-  </si>
-  <si>
-    <t>B0CYLXC8BQ</t>
-  </si>
-  <si>
     <t>B0D3M13T6H</t>
   </si>
   <si>
@@ -1487,9 +1424,6 @@
     <t>AA-01</t>
   </si>
   <si>
-    <t>AH-60 BL</t>
-  </si>
-  <si>
     <t>AM-W13</t>
   </si>
   <si>
@@ -1508,9 +1442,6 @@
     <t>AM-W47 Wireless</t>
   </si>
   <si>
-    <t>AH-60 RD</t>
-  </si>
-  <si>
     <t>AM-C3</t>
   </si>
   <si>
@@ -1556,9 +1487,6 @@
     <t>AM-W35</t>
   </si>
   <si>
-    <t>AM-Mix8</t>
-  </si>
-  <si>
     <t>AM-W23</t>
   </si>
   <si>
@@ -1724,9 +1652,6 @@
     <t>XM-24</t>
   </si>
   <si>
-    <t>A2-XLR</t>
-  </si>
-  <si>
     <t>AI-06</t>
   </si>
   <si>
@@ -1742,9 +1667,6 @@
     <t>AK-61 Pro</t>
   </si>
   <si>
-    <t>AM-W48</t>
-  </si>
-  <si>
     <t>A3-XLR</t>
   </si>
   <si>
@@ -1880,15 +1802,6 @@
     <t>AM-C14</t>
   </si>
   <si>
-    <t>AM-W44</t>
-  </si>
-  <si>
-    <t>AM-W42</t>
-  </si>
-  <si>
-    <t>AM-W38</t>
-  </si>
-  <si>
     <t>AA-09</t>
   </si>
   <si>
@@ -1910,18 +1823,6 @@
     <t>AA-13</t>
   </si>
   <si>
-    <t>AM-W39</t>
-  </si>
-  <si>
-    <t>AM-W40</t>
-  </si>
-  <si>
-    <t>AM-W41</t>
-  </si>
-  <si>
-    <t>AM-W43</t>
-  </si>
-  <si>
     <t>AA-16</t>
   </si>
   <si>
@@ -1931,24 +1832,6 @@
     <t>AA-24</t>
   </si>
   <si>
-    <t>AK-S1</t>
-  </si>
-  <si>
-    <t>AK-S2</t>
-  </si>
-  <si>
-    <t>AB-06</t>
-  </si>
-  <si>
-    <t>AB-07</t>
-  </si>
-  <si>
-    <t>AB-08</t>
-  </si>
-  <si>
-    <t>AB-09</t>
-  </si>
-  <si>
     <t>AWB-01</t>
   </si>
   <si>
@@ -1973,9 +1856,6 @@
     <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
   </si>
   <si>
-    <t>ASIN Not created</t>
-  </si>
-  <si>
     <t>B0GNM35G8X</t>
   </si>
   <si>
@@ -2240,9 +2120,6 @@
     <t>B0FN4DSQ6P</t>
   </si>
   <si>
-    <t>B0FN4GJ9S1</t>
-  </si>
-  <si>
     <t>B0FN4HDM6Z</t>
   </si>
   <si>
@@ -2571,6 +2448,27 @@
   </si>
   <si>
     <t>B0GTZ9X8Q2</t>
+  </si>
+  <si>
+    <t>AI-02 2x2| Metallic Red</t>
+  </si>
+  <si>
+    <t>AH-60-RD</t>
+  </si>
+  <si>
+    <t>AH-60-BL</t>
+  </si>
+  <si>
+    <t>B0FHVWHQHR</t>
+  </si>
+  <si>
+    <t>AM-Pro8</t>
+  </si>
+  <si>
+    <t>AM-S1 Bookshelf Speaker</t>
+  </si>
+  <si>
+    <t>AM-W48 / AM-S6</t>
   </si>
 </sst>
 </file>
@@ -2668,7 +2566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2697,6 +2595,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3524,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
-  <dimension ref="A1:O226"/>
+  <dimension ref="A1:O212"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3557,19 +3458,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>647</v>
+        <v>607</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>5</v>
@@ -3587,7 +3488,7 @@
         <v>9</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>649</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -3595,19 +3496,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>806</v>
+        <v>765</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G2" s="2">
         <v>5000</v>
@@ -3642,19 +3543,19 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -3679,19 +3580,19 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>808</v>
+        <v>767</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -3716,19 +3617,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>432</v>
+        <v>408</v>
+      </c>
+      <c r="D5" t="s">
+        <v>808</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>808</v>
+        <v>767</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -3753,19 +3654,19 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3790,19 +3691,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3827,19 +3728,19 @@
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -3864,19 +3765,19 @@
         <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3901,19 +3802,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>811</v>
+        <v>770</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3938,19 +3839,19 @@
         <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>806</v>
+        <v>765</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3975,19 +3876,19 @@
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -4012,19 +3913,19 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>808</v>
+        <v>767</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -4049,19 +3950,19 @@
         <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4086,19 +3987,19 @@
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -4123,19 +4024,19 @@
         <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -4160,19 +4061,19 @@
         <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -4197,19 +4098,19 @@
         <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -4234,17 +4135,17 @@
         <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -4269,19 +4170,19 @@
         <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -4306,19 +4207,19 @@
         <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -4343,19 +4244,19 @@
         <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -4380,19 +4281,19 @@
         <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>450</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>806</v>
+        <v>765</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -4417,17 +4318,17 @@
         <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -4452,19 +4353,19 @@
         <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -4489,19 +4390,19 @@
         <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4526,19 +4427,19 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>813</v>
+        <v>772</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -4563,19 +4464,19 @@
         <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4600,17 +4501,17 @@
         <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4635,19 +4536,19 @@
         <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4672,17 +4573,17 @@
         <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4707,17 +4608,17 @@
         <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4742,19 +4643,19 @@
         <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4779,19 +4680,19 @@
         <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4816,17 +4717,17 @@
         <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -4851,19 +4752,19 @@
         <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -4888,19 +4789,19 @@
         <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -4925,19 +4826,19 @@
         <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -4962,19 +4863,19 @@
         <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4999,19 +4900,19 @@
         <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -5036,19 +4937,19 @@
         <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -5073,19 +4974,19 @@
         <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>806</v>
+        <v>765</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -5110,17 +5011,17 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -5145,17 +5046,17 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -5180,19 +5081,19 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -5217,19 +5118,19 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>811</v>
+        <v>770</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -5254,19 +5155,19 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -5291,19 +5192,19 @@
         <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -5328,19 +5229,19 @@
         <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -5365,19 +5266,19 @@
         <v>58</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -5402,19 +5303,19 @@
         <v>59</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -5439,19 +5340,19 @@
         <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -5476,19 +5377,19 @@
         <v>61</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -5513,19 +5414,19 @@
         <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -5550,19 +5451,19 @@
         <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>482</v>
+        <v>805</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -5587,19 +5488,19 @@
         <v>64</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -5624,19 +5525,19 @@
         <v>65</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -5661,19 +5562,19 @@
         <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -5698,19 +5599,19 @@
         <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -5735,19 +5636,19 @@
         <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -5772,19 +5673,19 @@
         <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>815</v>
+        <v>774</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -5809,19 +5710,19 @@
         <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>489</v>
+        <v>408</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>804</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -5846,19 +5747,19 @@
         <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -5883,19 +5784,19 @@
         <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -5920,19 +5821,19 @@
         <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -5957,19 +5858,19 @@
         <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5994,19 +5895,19 @@
         <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -6031,17 +5932,17 @@
         <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -6066,19 +5967,19 @@
         <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -6103,19 +6004,19 @@
         <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>816</v>
+        <v>775</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -6140,17 +6041,17 @@
         <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -6175,17 +6076,17 @@
         <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -6210,19 +6111,19 @@
         <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -6247,19 +6148,19 @@
         <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>813</v>
+        <v>772</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -6284,19 +6185,19 @@
         <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -6321,19 +6222,19 @@
         <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -6358,19 +6259,19 @@
         <v>85</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -6395,19 +6296,19 @@
         <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -6432,17 +6333,17 @@
         <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>505</v>
+        <v>408</v>
+      </c>
+      <c r="D79" t="s">
+        <v>807</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -6467,19 +6368,19 @@
         <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -6504,19 +6405,19 @@
         <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -6541,19 +6442,19 @@
         <v>90</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -6578,19 +6479,19 @@
         <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -6615,19 +6516,19 @@
         <v>92</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -6652,19 +6553,19 @@
         <v>93</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -6689,19 +6590,19 @@
         <v>94</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -6726,19 +6627,19 @@
         <v>95</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>813</v>
+        <v>772</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -6763,19 +6664,19 @@
         <v>96</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>815</v>
+        <v>774</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -6800,19 +6701,19 @@
         <v>97</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -6837,19 +6738,19 @@
         <v>98</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>817</v>
+        <v>776</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -6874,19 +6775,19 @@
         <v>99</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>817</v>
+        <v>776</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -6911,17 +6812,17 @@
         <v>100</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -6946,19 +6847,19 @@
         <v>101</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -6983,17 +6884,17 @@
         <v>102</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -7018,19 +6919,19 @@
         <v>103</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -7055,17 +6956,17 @@
         <v>104</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -7090,19 +6991,19 @@
         <v>105</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -7127,17 +7028,17 @@
         <v>106</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -7162,19 +7063,19 @@
         <v>107</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -7199,19 +7100,19 @@
         <v>108</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -7236,19 +7137,19 @@
         <v>109</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -7273,19 +7174,19 @@
         <v>110</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -7310,19 +7211,19 @@
         <v>111</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -7347,17 +7248,17 @@
         <v>112</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -7382,19 +7283,19 @@
         <v>113</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -7419,19 +7320,19 @@
         <v>114</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -7456,19 +7357,19 @@
         <v>115</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -7493,17 +7394,17 @@
         <v>116</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -7528,19 +7429,19 @@
         <v>117</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -7565,17 +7466,17 @@
         <v>118</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -7600,19 +7501,19 @@
         <v>119</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>534</v>
+        <v>510</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -7637,19 +7538,19 @@
         <v>120</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -7674,17 +7575,17 @@
         <v>121</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -7709,19 +7610,19 @@
         <v>122</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -7746,19 +7647,19 @@
         <v>123</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -7783,19 +7684,19 @@
         <v>124</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -7820,17 +7721,17 @@
         <v>125</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -7855,19 +7756,19 @@
         <v>126</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>824</v>
+        <v>783</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -7892,19 +7793,19 @@
         <v>127</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>825</v>
+        <v>784</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -7929,19 +7830,19 @@
         <v>128</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>826</v>
+        <v>785</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -7966,19 +7867,19 @@
         <v>129</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>827</v>
+        <v>786</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -8003,19 +7904,19 @@
         <v>130</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>828</v>
+        <v>787</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -8040,19 +7941,19 @@
         <v>131</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -8077,19 +7978,19 @@
         <v>132</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>829</v>
+        <v>788</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -8114,19 +8015,19 @@
         <v>133</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>830</v>
+        <v>789</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -8151,19 +8052,19 @@
         <v>134</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>831</v>
+        <v>790</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -8188,19 +8089,19 @@
         <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>832</v>
+        <v>791</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -8225,19 +8126,19 @@
         <v>136</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>833</v>
+        <v>792</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -8262,19 +8163,19 @@
         <v>137</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>834</v>
+        <v>793</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -8299,19 +8200,19 @@
         <v>138</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>835</v>
+        <v>794</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -8336,19 +8237,19 @@
         <v>139</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>836</v>
+        <v>795</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -8373,19 +8274,19 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>837</v>
+        <v>796</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -8410,19 +8311,19 @@
         <v>141</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>838</v>
+        <v>797</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>819</v>
+        <v>778</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -8447,19 +8348,19 @@
         <v>142</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>839</v>
+        <v>798</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -8484,19 +8385,19 @@
         <v>143</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>840</v>
+        <v>799</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -8521,19 +8422,19 @@
         <v>144</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>841</v>
+        <v>800</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -8558,19 +8459,19 @@
         <v>145</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>842</v>
+        <v>801</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -8595,19 +8496,19 @@
         <v>146</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -8632,19 +8533,19 @@
         <v>147</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>807</v>
+        <v>766</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -8669,19 +8570,19 @@
         <v>148</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>644</v>
+        <v>338</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>561</v>
+        <v>510</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>813</v>
+        <v>766</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -8698,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
@@ -8706,19 +8607,19 @@
         <v>149</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -8735,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
@@ -8743,19 +8644,19 @@
         <v>150</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>806</v>
+        <v>779</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -8772,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
@@ -8780,19 +8681,19 @@
         <v>151</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>820</v>
+        <v>779</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -8809,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
@@ -8817,19 +8718,19 @@
         <v>152</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>820</v>
+        <v>779</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -8846,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
@@ -8854,19 +8755,19 @@
         <v>153</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>820</v>
+        <v>779</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -8891,19 +8792,17 @@
         <v>154</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>357</v>
+        <v>606</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>820</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="D146" t="s">
+        <v>809</v>
+      </c>
+      <c r="E146" s="4"/>
       <c r="F146" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -8928,17 +8827,19 @@
         <v>155</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>646</v>
+        <v>344</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="E147" s="4"/>
+        <v>542</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>772</v>
+      </c>
       <c r="F147" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -8963,19 +8864,19 @@
         <v>156</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>358</v>
+        <v>605</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>568</v>
+        <v>543</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -9000,19 +8901,19 @@
         <v>157</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>645</v>
+        <v>345</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>569</v>
+        <v>544</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>821</v>
+        <v>767</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -9029,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
@@ -9037,19 +8938,19 @@
         <v>158</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>570</v>
+        <v>491</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>808</v>
+        <v>766</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -9066,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
@@ -9074,19 +8975,17 @@
         <v>159</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="E151" s="4"/>
       <c r="F151" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -9103,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="3">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
@@ -9111,17 +9010,19 @@
         <v>160</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="E152" s="4"/>
+        <v>546</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>771</v>
+      </c>
       <c r="F152" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -9138,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
@@ -9146,19 +9047,17 @@
         <v>161</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>812</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="E153" s="4"/>
       <c r="F153" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -9175,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
@@ -9183,17 +9082,19 @@
         <v>162</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="E154" s="4"/>
+        <v>548</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>767</v>
+      </c>
       <c r="F154" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -9210,7 +9111,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
@@ -9218,19 +9119,19 @@
         <v>163</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>808</v>
+        <v>766</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -9255,19 +9156,17 @@
         <v>164</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="E156" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="E156" s="4"/>
       <c r="F156" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -9284,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
@@ -9292,17 +9191,19 @@
         <v>165</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="E157" s="4"/>
+        <v>551</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F157" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -9319,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
@@ -9327,19 +9228,19 @@
         <v>166</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>577</v>
+        <v>803</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -9356,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
@@ -9364,19 +9265,19 @@
         <v>167</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>617</v>
+        <v>552</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>806</v>
+        <v>766</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -9393,7 +9294,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
@@ -9401,19 +9302,17 @@
         <v>168</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="E160" s="4"/>
       <c r="F160" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -9430,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
@@ -9438,17 +9337,17 @@
         <v>169</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -9473,17 +9372,19 @@
         <v>170</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="E162" s="4"/>
+        <v>555</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F162" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -9500,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="3">
-        <v>100</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
@@ -9508,19 +9409,17 @@
         <v>171</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="E163" s="4"/>
       <c r="F163" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -9537,7 +9436,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
@@ -9545,17 +9444,17 @@
         <v>172</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -9572,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
@@ -9580,17 +9479,19 @@
         <v>173</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="E165" s="4"/>
+        <v>558</v>
+      </c>
+      <c r="E165" s="4" t="s">
+        <v>777</v>
+      </c>
       <c r="F165" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -9607,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
@@ -9615,19 +9516,17 @@
         <v>174</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>818</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="E166" s="4"/>
       <c r="F166" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -9644,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
@@ -9652,17 +9551,17 @@
         <v>175</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
@@ -9687,17 +9586,17 @@
         <v>176</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>586</v>
+        <v>561</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -9722,17 +9621,17 @@
         <v>177</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -9749,7 +9648,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
@@ -9757,17 +9656,17 @@
         <v>178</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
@@ -9784,7 +9683,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="3">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
@@ -9792,17 +9691,19 @@
         <v>179</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="E171" s="4"/>
+        <v>564</v>
+      </c>
+      <c r="E171" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F171" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -9819,7 +9720,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
@@ -9827,19 +9728,17 @@
         <v>180</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="E172" s="4"/>
       <c r="F172" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -9856,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
@@ -9864,17 +9763,17 @@
         <v>181</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>591</v>
+        <v>566</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
@@ -9891,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
@@ -9899,17 +9798,19 @@
         <v>182</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="E174" s="4"/>
+        <v>567</v>
+      </c>
+      <c r="E174" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F174" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
@@ -9926,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="O174" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
@@ -9934,19 +9835,19 @@
         <v>183</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>593</v>
+        <v>568</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>807</v>
+        <v>771</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -9963,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="O175" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
@@ -9971,19 +9872,19 @@
         <v>184</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -10000,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="O176" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
@@ -10008,19 +9909,19 @@
         <v>185</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>812</v>
+        <v>781</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -10045,19 +9946,17 @@
         <v>186</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="E178" s="4" t="s">
-        <v>822</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -10074,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="O178" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
@@ -10082,17 +9981,17 @@
         <v>187</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -10109,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="O179" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
@@ -10117,17 +10016,19 @@
         <v>188</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="E180" s="4"/>
+        <v>573</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F180" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -10144,7 +10045,7 @@
         <v>0</v>
       </c>
       <c r="O180" s="3">
-        <v>8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
@@ -10152,19 +10053,19 @@
         <v>189</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>807</v>
+        <v>771</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
@@ -10181,7 +10082,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="3">
-        <v>100</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
@@ -10189,19 +10090,19 @@
         <v>190</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>812</v>
+        <v>766</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
@@ -10218,7 +10119,7 @@
         <v>0</v>
       </c>
       <c r="O182" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
@@ -10226,19 +10127,17 @@
         <v>191</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="E183" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E183" s="4"/>
       <c r="F183" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
@@ -10255,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="O183" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
@@ -10263,17 +10162,19 @@
         <v>192</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="E184" s="4"/>
+        <v>577</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>781</v>
+      </c>
       <c r="F184" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
@@ -10290,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="O184" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
@@ -10298,19 +10199,19 @@
         <v>193</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>822</v>
+        <v>781</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
@@ -10335,19 +10236,17 @@
         <v>194</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E186" s="4" t="s">
-        <v>822</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="E186" s="4"/>
       <c r="F186" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
@@ -10364,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="O186" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -10372,17 +10271,17 @@
         <v>195</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
@@ -10407,17 +10306,17 @@
         <v>196</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
@@ -10434,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="O188" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.3">
@@ -10442,17 +10341,17 @@
         <v>197</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
@@ -10469,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.3">
@@ -10477,17 +10376,17 @@
         <v>198</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
@@ -10504,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="O190" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.3">
@@ -10512,17 +10411,19 @@
         <v>199</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="E191" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>765</v>
+      </c>
       <c r="F191" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
@@ -10539,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="O191" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.3">
@@ -10547,19 +10448,17 @@
         <v>200</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="E192" s="4" t="s">
-        <v>806</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="E192" s="4"/>
       <c r="F192" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
@@ -10576,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="O192" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.3">
@@ -10584,17 +10483,17 @@
         <v>201</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="E193" s="4"/>
       <c r="F193" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
@@ -10611,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="O193" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.3">
@@ -10619,17 +10518,17 @@
         <v>202</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="E194" s="4"/>
       <c r="F194" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
@@ -10646,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="O194" s="3">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.3">
@@ -10654,17 +10553,17 @@
         <v>203</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -10681,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="O195" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.3">
@@ -10689,17 +10588,19 @@
         <v>204</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="E196" s="4"/>
+        <v>589</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>766</v>
+      </c>
       <c r="F196" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -10716,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="O196" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.3">
@@ -10724,17 +10625,17 @@
         <v>205</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -10751,7 +10652,7 @@
         <v>0</v>
       </c>
       <c r="O197" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.3">
@@ -10759,17 +10660,19 @@
         <v>206</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E198" s="4"/>
+        <v>591</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>771</v>
+      </c>
       <c r="F198" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -10786,7 +10689,7 @@
         <v>0</v>
       </c>
       <c r="O198" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.3">
@@ -10794,17 +10697,17 @@
         <v>207</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
@@ -10821,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="O199" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.3">
@@ -10829,19 +10732,17 @@
         <v>208</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="E200" s="4" t="s">
-        <v>807</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="E200" s="4"/>
       <c r="F200" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -10858,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="O200" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.3">
@@ -10866,17 +10767,19 @@
         <v>209</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="E201" s="4"/>
+        <v>594</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>771</v>
+      </c>
       <c r="F201" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -10893,7 +10796,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
@@ -10901,19 +10804,19 @@
         <v>210</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>812</v>
+        <v>771</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -10938,17 +10841,19 @@
         <v>211</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="E203" s="4"/>
+        <v>596</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>771</v>
+      </c>
       <c r="F203" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -10965,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.3">
@@ -10973,17 +10878,19 @@
         <v>212</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="E204" s="4"/>
+        <v>597</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>777</v>
+      </c>
       <c r="F204" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -11000,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.3">
@@ -11008,17 +10915,17 @@
         <v>213</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>644</v>
+        <v>401</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>623</v>
+        <v>598</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -11035,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.3">
@@ -11043,17 +10950,17 @@
         <v>214</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>644</v>
+        <v>402</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>624</v>
+        <v>599</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
@@ -11070,7 +10977,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.3">
@@ -11078,17 +10985,17 @@
         <v>215</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>644</v>
+        <v>403</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -11105,7 +11012,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.3">
@@ -11113,17 +11020,17 @@
         <v>216</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>644</v>
+        <v>404</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>626</v>
+        <v>601</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
@@ -11140,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.3">
@@ -11148,19 +11055,17 @@
         <v>217</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="E209" s="4" t="s">
-        <v>812</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
@@ -11177,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.3">
@@ -11185,19 +11090,17 @@
         <v>218</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="E210" s="4" t="s">
-        <v>812</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
@@ -11214,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.3">
@@ -11222,19 +11125,17 @@
         <v>219</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="E211" s="4" t="s">
-        <v>812</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
@@ -11251,632 +11152,140 @@
         <v>0</v>
       </c>
       <c r="O211" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A212" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="E212" s="4"/>
-      <c r="F212" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2">
-        <v>0</v>
-      </c>
-      <c r="J212" s="2"/>
-      <c r="K212" s="2"/>
-      <c r="L212" s="2"/>
-      <c r="M212" s="2">
-        <v>0</v>
-      </c>
-      <c r="N212" s="2">
-        <v>0</v>
-      </c>
-      <c r="O212" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A213" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2">
-        <v>0</v>
-      </c>
-      <c r="J213" s="2"/>
-      <c r="K213" s="2"/>
-      <c r="L213" s="2"/>
-      <c r="M213" s="2">
-        <v>0</v>
-      </c>
-      <c r="N213" s="2">
-        <v>0</v>
-      </c>
-      <c r="O213" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A214" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D214" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2">
-        <v>0</v>
-      </c>
-      <c r="J214" s="2"/>
-      <c r="K214" s="2"/>
-      <c r="L214" s="2"/>
-      <c r="M214" s="2">
-        <v>0</v>
-      </c>
-      <c r="N214" s="2">
-        <v>0</v>
-      </c>
-      <c r="O214" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A215" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="E215" s="4"/>
-      <c r="F215" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2">
-        <v>0</v>
-      </c>
-      <c r="J215" s="2"/>
-      <c r="K215" s="2"/>
-      <c r="L215" s="2"/>
-      <c r="M215" s="2">
-        <v>0</v>
-      </c>
-      <c r="N215" s="2">
-        <v>0</v>
-      </c>
-      <c r="O215" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A216" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G216" s="2"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2">
-        <v>0</v>
-      </c>
-      <c r="J216" s="2"/>
-      <c r="K216" s="2"/>
-      <c r="L216" s="2"/>
-      <c r="M216" s="2">
-        <v>0</v>
-      </c>
-      <c r="N216" s="2">
-        <v>0</v>
-      </c>
-      <c r="O216" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A217" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G217" s="2"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2">
-        <v>0</v>
-      </c>
-      <c r="J217" s="2"/>
-      <c r="K217" s="2"/>
-      <c r="L217" s="2"/>
-      <c r="M217" s="2">
-        <v>0</v>
-      </c>
-      <c r="N217" s="2">
-        <v>0</v>
-      </c>
-      <c r="O217" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A218" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="E218" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="F218" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G218" s="2"/>
-      <c r="H218" s="2"/>
-      <c r="I218" s="2">
-        <v>0</v>
-      </c>
-      <c r="J218" s="2"/>
-      <c r="K218" s="2"/>
-      <c r="L218" s="2"/>
-      <c r="M218" s="2">
-        <v>0</v>
-      </c>
-      <c r="N218" s="2">
-        <v>0</v>
-      </c>
-      <c r="O218" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D219" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="E219" s="4"/>
-      <c r="F219" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G219" s="2"/>
-      <c r="H219" s="2"/>
-      <c r="I219" s="2">
-        <v>0</v>
-      </c>
-      <c r="J219" s="2"/>
-      <c r="K219" s="2"/>
-      <c r="L219" s="2"/>
-      <c r="M219" s="2">
-        <v>0</v>
-      </c>
-      <c r="N219" s="2">
-        <v>0</v>
-      </c>
-      <c r="O219" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A220" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="E220" s="4"/>
-      <c r="F220" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2">
-        <v>0</v>
-      </c>
-      <c r="J220" s="2"/>
-      <c r="K220" s="2"/>
-      <c r="L220" s="2"/>
-      <c r="M220" s="2">
-        <v>0</v>
-      </c>
-      <c r="N220" s="2">
-        <v>0</v>
-      </c>
-      <c r="O220" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A221" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D221" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2">
-        <v>0</v>
-      </c>
-      <c r="J221" s="2"/>
-      <c r="K221" s="2"/>
-      <c r="L221" s="2"/>
-      <c r="M221" s="2">
-        <v>0</v>
-      </c>
-      <c r="N221" s="2">
-        <v>0</v>
-      </c>
-      <c r="O221" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A222" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2">
-        <v>0</v>
-      </c>
-      <c r="J222" s="2"/>
-      <c r="K222" s="2"/>
-      <c r="L222" s="2"/>
-      <c r="M222" s="2">
-        <v>0</v>
-      </c>
-      <c r="N222" s="2">
-        <v>0</v>
-      </c>
-      <c r="O222" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A223" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D223" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="E223" s="4"/>
-      <c r="F223" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2">
-        <v>0</v>
-      </c>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2"/>
-      <c r="M223" s="2">
-        <v>0</v>
-      </c>
-      <c r="N223" s="2">
-        <v>0</v>
-      </c>
-      <c r="O223" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A224" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="E224" s="4"/>
-      <c r="F224" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2">
-        <v>0</v>
-      </c>
-      <c r="J224" s="2"/>
-      <c r="K224" s="2"/>
-      <c r="L224" s="2"/>
-      <c r="M224" s="2">
-        <v>0</v>
-      </c>
-      <c r="N224" s="2">
-        <v>0</v>
-      </c>
-      <c r="O224" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A225" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D225" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2">
-        <v>0</v>
-      </c>
-      <c r="J225" s="2"/>
-      <c r="K225" s="2"/>
-      <c r="L225" s="2"/>
-      <c r="M225" s="2">
-        <v>0</v>
-      </c>
-      <c r="N225" s="2">
-        <v>0</v>
-      </c>
-      <c r="O225" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O225" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}"/>
+  <autoFilter ref="A1:O211" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}"/>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="50" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="49" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:A10">
-    <cfRule type="duplicateValues" dxfId="48" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:A43">
-    <cfRule type="duplicateValues" dxfId="47" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A54 A36">
-    <cfRule type="duplicateValues" dxfId="46" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:A54">
-    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:A59">
-    <cfRule type="duplicateValues" dxfId="44" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60">
-    <cfRule type="duplicateValues" dxfId="43" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="42" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62">
-    <cfRule type="duplicateValues" dxfId="41" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A91">
-    <cfRule type="duplicateValues" dxfId="40" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="39" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A110">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A134">
-    <cfRule type="duplicateValues" dxfId="34" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="33" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A148:A156">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="43"/>
+  <conditionalFormatting sqref="A147:A155">
+    <cfRule type="duplicateValues" dxfId="31" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A157:A158">
-    <cfRule type="duplicateValues" dxfId="29" priority="41"/>
+  <conditionalFormatting sqref="A156:A157">
+    <cfRule type="duplicateValues" dxfId="29" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B226">
-    <cfRule type="duplicateValues" dxfId="23" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="48"/>
+  <conditionalFormatting sqref="A2:B212">
+    <cfRule type="duplicateValues" dxfId="28" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4 B6:B8 B147:B192 B11:B140">
-    <cfRule type="duplicateValues" dxfId="21" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B4 B6:B225">
-    <cfRule type="duplicateValues" dxfId="20" priority="53"/>
+  <conditionalFormatting sqref="B2:B4 B6:B211">
+    <cfRule type="duplicateValues" dxfId="26" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="19" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:B43">
-    <cfRule type="duplicateValues" dxfId="18" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:B54 B36">
-    <cfRule type="duplicateValues" dxfId="17" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:B54">
-    <cfRule type="duplicateValues" dxfId="16" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:B59">
-    <cfRule type="duplicateValues" dxfId="15" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="14" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="13" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="12" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="11" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="10" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139:B140">
-    <cfRule type="duplicateValues" dxfId="9" priority="66"/>
+  <conditionalFormatting sqref="B139">
+    <cfRule type="duplicateValues" dxfId="15" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B140">
+    <cfRule type="duplicateValues" dxfId="14" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="8" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="6" priority="69"/>
+  <conditionalFormatting sqref="B141:B146">
+    <cfRule type="duplicateValues" dxfId="11" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142:B147">
-    <cfRule type="duplicateValues" dxfId="5" priority="70"/>
+  <conditionalFormatting sqref="B142:B145">
+    <cfRule type="duplicateValues" dxfId="10" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143:B146">
-    <cfRule type="duplicateValues" dxfId="4" priority="71"/>
+  <conditionalFormatting sqref="B146">
+    <cfRule type="duplicateValues" dxfId="9" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="3" priority="72"/>
+  <conditionalFormatting sqref="B146:B191 B2:B4 B6:B8 B11:B139">
+    <cfRule type="duplicateValues" dxfId="8" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148:B151">
-    <cfRule type="duplicateValues" dxfId="2" priority="73"/>
+  <conditionalFormatting sqref="B147:B150">
+    <cfRule type="duplicateValues" dxfId="7" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152:B156">
-    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+  <conditionalFormatting sqref="B151:B155">
+    <cfRule type="duplicateValues" dxfId="6" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157:B158">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  <conditionalFormatting sqref="B156:B157">
+    <cfRule type="duplicateValues" dxfId="5" priority="75"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11905,22 +11314,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>797</v>
+        <v>756</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>823</v>
+        <v>782</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>647</v>
+        <v>607</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>5</v>
@@ -11938,33 +11347,33 @@
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>649</v>
+        <v>609</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>802</v>
+        <v>761</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>803</v>
+        <v>762</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>695</v>
+        <v>655</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>737</v>
+        <v>696</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>779</v>
+        <v>738</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>779</v>
+        <v>738</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G2" s="2">
         <v>1000</v>
@@ -11997,33 +11406,33 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q2" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R2" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>696</v>
+        <v>656</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>738</v>
+        <v>697</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -12037,33 +11446,33 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q3" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R3" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>780</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -12077,33 +11486,33 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q4" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R4" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>657</v>
+        <v>617</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>698</v>
+        <v>658</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>740</v>
+        <v>699</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -12117,33 +11526,33 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q5" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R5" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>658</v>
+        <v>618</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>699</v>
+        <v>659</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>741</v>
+        <v>700</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -12157,33 +11566,33 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q6" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R6" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>659</v>
+        <v>619</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>783</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -12197,33 +11606,33 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q7" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R7" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>660</v>
+        <v>620</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>701</v>
+        <v>661</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>743</v>
+        <v>702</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -12237,33 +11646,33 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q8" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R8" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>661</v>
+        <v>621</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>662</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>744</v>
+        <v>703</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -12277,33 +11686,33 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q9" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R9" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>703</v>
+        <v>663</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>745</v>
+        <v>704</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -12317,33 +11726,33 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q10" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R10" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>746</v>
+        <v>705</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -12357,33 +11766,33 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q11" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R11" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>664</v>
+        <v>624</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>705</v>
+        <v>665</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>747</v>
+        <v>706</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -12397,33 +11806,33 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q12" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R12" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>706</v>
+        <v>666</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>748</v>
+        <v>707</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -12437,33 +11846,33 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q13" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R13" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>666</v>
+        <v>626</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>707</v>
+        <v>667</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>749</v>
+        <v>708</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -12477,33 +11886,33 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q14" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R14" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>667</v>
+        <v>627</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>708</v>
+        <v>668</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>750</v>
+        <v>709</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -12517,33 +11926,33 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q15" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R15" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>668</v>
+        <v>628</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>709</v>
+        <v>669</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>751</v>
+        <v>710</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -12557,33 +11966,33 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q16" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R16" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>669</v>
+        <v>629</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>752</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -12597,33 +12006,33 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q17" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R17" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>670</v>
+        <v>630</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>711</v>
+        <v>671</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>753</v>
+        <v>712</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -12637,33 +12046,33 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q18" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R18" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>669</v>
+        <v>629</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>752</v>
+        <v>711</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -12677,33 +12086,33 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q19" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R19" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>668</v>
+        <v>628</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>709</v>
+        <v>669</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>751</v>
+        <v>710</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -12717,33 +12126,33 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q20" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R20" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>671</v>
+        <v>631</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>712</v>
+        <v>672</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>754</v>
+        <v>713</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -12757,33 +12166,33 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q21" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R21" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>672</v>
+        <v>632</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>713</v>
+        <v>673</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>755</v>
+        <v>714</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -12797,33 +12206,33 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q22" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R22" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>673</v>
+        <v>633</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>714</v>
+        <v>674</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>756</v>
+        <v>715</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -12837,33 +12246,33 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q23" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R23" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -12877,33 +12286,33 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q24" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R24" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>758</v>
+        <v>717</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>785</v>
+        <v>744</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -12917,33 +12326,33 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="Q25" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="R25" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>676</v>
+        <v>636</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>759</v>
+        <v>718</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>786</v>
+        <v>745</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -12957,33 +12366,33 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q26" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R26" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>677</v>
+        <v>637</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>718</v>
+        <v>678</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>760</v>
+        <v>719</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>786</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -12997,33 +12406,33 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q27" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R27" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>719</v>
+        <v>679</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>761</v>
+        <v>720</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>787</v>
+        <v>746</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -13037,33 +12446,33 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q28" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R28" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>679</v>
+        <v>639</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>762</v>
+        <v>721</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>787</v>
+        <v>746</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>798</v>
+        <v>757</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -13077,33 +12486,33 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q29" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R29" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>721</v>
+        <v>681</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>763</v>
+        <v>722</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>788</v>
+        <v>747</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -13117,33 +12526,33 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q30" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R30" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>681</v>
+        <v>641</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>722</v>
+        <v>682</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>764</v>
+        <v>723</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>789</v>
+        <v>748</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -13157,33 +12566,33 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q31" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R31" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>682</v>
+        <v>642</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>765</v>
+        <v>724</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>789</v>
+        <v>748</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -13197,33 +12606,33 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q32" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R32" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>683</v>
+        <v>643</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>724</v>
+        <v>684</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>766</v>
+        <v>725</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>790</v>
+        <v>749</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -13237,33 +12646,33 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q33" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R33" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>684</v>
+        <v>644</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>725</v>
+        <v>685</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>767</v>
+        <v>726</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>791</v>
+        <v>750</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -13277,33 +12686,33 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q34" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R34" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>685</v>
+        <v>645</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>726</v>
+        <v>686</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>768</v>
+        <v>727</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>792</v>
+        <v>751</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -13317,33 +12726,33 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q35" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R35" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>686</v>
+        <v>646</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>727</v>
+        <v>687</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>769</v>
+        <v>728</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -13360,30 +12769,30 @@
         <v>9</v>
       </c>
       <c r="Q36" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R36" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>687</v>
+        <v>647</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>728</v>
+        <v>688</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>770</v>
+        <v>729</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -13400,30 +12809,30 @@
         <v>9</v>
       </c>
       <c r="Q37" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R37" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>729</v>
+        <v>689</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>771</v>
+        <v>730</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>793</v>
+        <v>752</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -13440,30 +12849,30 @@
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R38" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>689</v>
+        <v>649</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>730</v>
+        <v>690</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>772</v>
+        <v>731</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -13480,30 +12889,30 @@
         <v>9</v>
       </c>
       <c r="Q39" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R39" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>690</v>
+        <v>650</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>731</v>
+        <v>691</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>773</v>
+        <v>732</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -13520,30 +12929,30 @@
         <v>9</v>
       </c>
       <c r="Q40" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R40" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>691</v>
+        <v>651</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>732</v>
+        <v>692</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -13560,30 +12969,30 @@
         <v>9</v>
       </c>
       <c r="Q41" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R41" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>733</v>
+        <v>758</v>
+      </c>
+      <c r="B42" t="s">
+        <v>806</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>775</v>
+        <v>734</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -13600,30 +13009,30 @@
         <v>9</v>
       </c>
       <c r="Q42" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R42" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>734</v>
+        <v>693</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>776</v>
+        <v>735</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>794</v>
+        <v>753</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -13640,30 +13049,30 @@
         <v>9</v>
       </c>
       <c r="Q43" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R43" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>735</v>
+        <v>694</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>795</v>
+        <v>754</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -13677,33 +13086,33 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q44" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R44" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>694</v>
+        <v>654</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>736</v>
+        <v>695</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>778</v>
+        <v>737</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>796</v>
+        <v>755</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -13717,26 +13126,26 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>801</v>
+        <v>760</v>
       </c>
       <c r="Q45" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="R45" t="s">
-        <v>804</v>
+        <v>763</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13:A15">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:A23">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:B45 B2:B15">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7387449E-FEC1-4802-8131-B7B5E005A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A678428-CF0E-4B65-8204-F33B36ABAE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -3425,6 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O212"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3491,7 +3492,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3612,7 +3613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3649,7 +3650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3723,7 +3724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3760,7 +3761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3797,7 +3798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3834,7 +3835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3871,7 +3872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3908,7 +3909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3982,7 +3983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4019,7 +4020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4093,7 +4094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4130,7 +4131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4165,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4202,7 +4203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4239,7 +4240,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4276,7 +4277,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -4348,7 +4349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4385,7 +4386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4422,7 +4423,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4459,7 +4460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4496,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -4531,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -4568,7 +4569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -4638,7 +4639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -4747,7 +4748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -4784,7 +4785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -4821,7 +4822,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -4895,7 +4896,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,7 +4933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -5006,7 +5007,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -5041,7 +5042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
@@ -5076,7 +5077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -5150,7 +5151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -5187,7 +5188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -5224,7 +5225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -5261,7 +5262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
@@ -5335,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
@@ -5372,7 +5373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
@@ -5409,7 +5410,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>62</v>
       </c>
@@ -5446,7 +5447,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>63</v>
       </c>
@@ -5483,7 +5484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>64</v>
       </c>
@@ -5520,7 +5521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>66</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>67</v>
       </c>
@@ -5631,7 +5632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -5742,7 +5743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
@@ -5779,7 +5780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>72</v>
       </c>
@@ -5816,7 +5817,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>73</v>
       </c>
@@ -5853,7 +5854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>74</v>
       </c>
@@ -5890,7 +5891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
@@ -5927,7 +5928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -5962,7 +5963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>77</v>
       </c>
@@ -5999,7 +6000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>78</v>
       </c>
@@ -6036,7 +6037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>79</v>
       </c>
@@ -6071,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>80</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>81</v>
       </c>
@@ -6143,7 +6144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>82</v>
       </c>
@@ -6180,7 +6181,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>83</v>
       </c>
@@ -6217,7 +6218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>84</v>
       </c>
@@ -6254,7 +6255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>85</v>
       </c>
@@ -6291,7 +6292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>86</v>
       </c>
@@ -6328,7 +6329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>87</v>
       </c>
@@ -6363,7 +6364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>88</v>
       </c>
@@ -6400,7 +6401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>89</v>
       </c>
@@ -6437,7 +6438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>90</v>
       </c>
@@ -6474,7 +6475,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>91</v>
       </c>
@@ -6511,7 +6512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>92</v>
       </c>
@@ -6548,7 +6549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>93</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>94</v>
       </c>
@@ -6622,7 +6623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>95</v>
       </c>
@@ -6659,7 +6660,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>96</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>97</v>
       </c>
@@ -6733,7 +6734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>98</v>
       </c>
@@ -6770,7 +6771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>99</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>100</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>101</v>
       </c>
@@ -6879,7 +6880,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>102</v>
       </c>
@@ -6914,7 +6915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>103</v>
       </c>
@@ -6951,7 +6952,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>104</v>
       </c>
@@ -6986,7 +6987,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>105</v>
       </c>
@@ -7023,7 +7024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>106</v>
       </c>
@@ -7058,7 +7059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>107</v>
       </c>
@@ -7095,7 +7096,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>108</v>
       </c>
@@ -7132,7 +7133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>109</v>
       </c>
@@ -7169,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>110</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>111</v>
       </c>
@@ -7243,7 +7244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>112</v>
       </c>
@@ -7278,7 +7279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>113</v>
       </c>
@@ -7315,7 +7316,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>114</v>
       </c>
@@ -7352,7 +7353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>115</v>
       </c>
@@ -7389,7 +7390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>116</v>
       </c>
@@ -7424,7 +7425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>117</v>
       </c>
@@ -7461,7 +7462,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>118</v>
       </c>
@@ -7496,7 +7497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>119</v>
       </c>
@@ -7533,7 +7534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>120</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>121</v>
       </c>
@@ -7605,7 +7606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>122</v>
       </c>
@@ -7642,7 +7643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>123</v>
       </c>
@@ -7679,7 +7680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>124</v>
       </c>
@@ -7716,7 +7717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>125</v>
       </c>
@@ -7751,7 +7752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>126</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>127</v>
       </c>
@@ -7825,7 +7826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>128</v>
       </c>
@@ -7862,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>129</v>
       </c>
@@ -7899,7 +7900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>130</v>
       </c>
@@ -7936,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>131</v>
       </c>
@@ -7973,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>132</v>
       </c>
@@ -8010,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>133</v>
       </c>
@@ -8047,7 +8048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>134</v>
       </c>
@@ -8084,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>135</v>
       </c>
@@ -8121,7 +8122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>136</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>137</v>
       </c>
@@ -8195,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>138</v>
       </c>
@@ -8232,7 +8233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>139</v>
       </c>
@@ -8269,7 +8270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>140</v>
       </c>
@@ -8306,7 +8307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -8343,7 +8344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>142</v>
       </c>
@@ -8380,7 +8381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>143</v>
       </c>
@@ -8417,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>144</v>
       </c>
@@ -8454,7 +8455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>145</v>
       </c>
@@ -8491,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>146</v>
       </c>
@@ -8528,7 +8529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>147</v>
       </c>
@@ -8565,7 +8566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>148</v>
       </c>
@@ -8602,7 +8603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>149</v>
       </c>
@@ -8639,7 +8640,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>150</v>
       </c>
@@ -8676,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>151</v>
       </c>
@@ -8713,7 +8714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>152</v>
       </c>
@@ -8750,7 +8751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>153</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>154</v>
       </c>
@@ -8822,7 +8823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>155</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>156</v>
       </c>
@@ -8896,7 +8897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>157</v>
       </c>
@@ -8933,7 +8934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>158</v>
       </c>
@@ -8970,7 +8971,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>159</v>
       </c>
@@ -9005,7 +9006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>160</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>161</v>
       </c>
@@ -9077,7 +9078,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>162</v>
       </c>
@@ -9114,7 +9115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>163</v>
       </c>
@@ -9151,7 +9152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>164</v>
       </c>
@@ -9186,7 +9187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>165</v>
       </c>
@@ -9223,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>166</v>
       </c>
@@ -9260,7 +9261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>167</v>
       </c>
@@ -9297,7 +9298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>168</v>
       </c>
@@ -9332,7 +9333,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>169</v>
       </c>
@@ -9367,7 +9368,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>170</v>
       </c>
@@ -9404,7 +9405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>171</v>
       </c>
@@ -9439,7 +9440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>172</v>
       </c>
@@ -9474,7 +9475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>173</v>
       </c>
@@ -9511,7 +9512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>174</v>
       </c>
@@ -9546,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>175</v>
       </c>
@@ -9581,7 +9582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>176</v>
       </c>
@@ -9616,7 +9617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>177</v>
       </c>
@@ -9651,7 +9652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>178</v>
       </c>
@@ -9686,7 +9687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>179</v>
       </c>
@@ -9723,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>180</v>
       </c>
@@ -9758,7 +9759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>181</v>
       </c>
@@ -9793,7 +9794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>182</v>
       </c>
@@ -9830,7 +9831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>183</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>184</v>
       </c>
@@ -9904,7 +9905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>185</v>
       </c>
@@ -9941,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>186</v>
       </c>
@@ -9976,7 +9977,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>187</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>188</v>
       </c>
@@ -10048,7 +10049,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>189</v>
       </c>
@@ -10085,7 +10086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>190</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>191</v>
       </c>
@@ -10157,7 +10158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>192</v>
       </c>
@@ -10194,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>193</v>
       </c>
@@ -10231,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>194</v>
       </c>
@@ -10266,7 +10267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>195</v>
       </c>
@@ -10301,7 +10302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>196</v>
       </c>
@@ -10336,7 +10337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>197</v>
       </c>
@@ -10371,7 +10372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>198</v>
       </c>
@@ -10406,7 +10407,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>199</v>
       </c>
@@ -10443,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>200</v>
       </c>
@@ -10478,7 +10479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>201</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>202</v>
       </c>
@@ -10548,7 +10549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>203</v>
       </c>
@@ -10583,7 +10584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>204</v>
       </c>
@@ -10620,7 +10621,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>205</v>
       </c>
@@ -10655,7 +10656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>206</v>
       </c>
@@ -10692,7 +10693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>207</v>
       </c>
@@ -10727,7 +10728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>208</v>
       </c>
@@ -10762,7 +10763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>209</v>
       </c>
@@ -10799,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>210</v>
       </c>
@@ -10836,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>211</v>
       </c>
@@ -10873,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>212</v>
       </c>
@@ -10910,7 +10911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>213</v>
       </c>
@@ -10945,7 +10946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>214</v>
       </c>
@@ -10980,7 +10981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>215</v>
       </c>
@@ -11015,7 +11016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>216</v>
       </c>
@@ -11050,7 +11051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>217</v>
       </c>
@@ -11085,7 +11086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>218</v>
       </c>
@@ -11120,7 +11121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>219</v>
       </c>
@@ -11160,7 +11161,13 @@
       <c r="B212" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O211" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}"/>
+  <autoFilter ref="A1:O211" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="AM-S1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="50" priority="102"/>
   </conditionalFormatting>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A678428-CF0E-4B65-8204-F33B36ABAE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48138569-E608-42B2-911B-A4F5C94C9E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -3425,7 +3425,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O212"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3492,7 +3491,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -3539,7 +3538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3724,7 +3723,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3872,7 +3871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4020,7 +4019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4094,7 +4093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4131,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4166,7 +4165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4203,7 +4202,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4240,7 +4239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4277,7 +4276,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -4314,7 +4313,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4386,7 +4385,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4423,7 +4422,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4460,7 +4459,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4497,7 +4496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -4604,7 +4603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -4639,7 +4638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -4713,7 +4712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -4748,7 +4747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -4785,7 +4784,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -4822,7 +4821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -4859,7 +4858,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>47</v>
       </c>
@@ -4896,7 +4895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,7 +4932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,7 +4969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -5007,7 +5006,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
@@ -5042,7 +5041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>52</v>
       </c>
@@ -5077,7 +5076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>53</v>
       </c>
@@ -5114,7 +5113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>54</v>
       </c>
@@ -5151,7 +5150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>55</v>
       </c>
@@ -5188,7 +5187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>56</v>
       </c>
@@ -5225,7 +5224,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -5262,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>58</v>
       </c>
@@ -5299,7 +5298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>60</v>
       </c>
@@ -5373,7 +5372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>61</v>
       </c>
@@ -5410,7 +5409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>62</v>
       </c>
@@ -5447,7 +5446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>63</v>
       </c>
@@ -5484,7 +5483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>64</v>
       </c>
@@ -5521,7 +5520,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -5558,7 +5557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>66</v>
       </c>
@@ -5595,7 +5594,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>67</v>
       </c>
@@ -5632,7 +5631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -5669,7 +5668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
@@ -5706,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -5743,7 +5742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
@@ -5780,7 +5779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>72</v>
       </c>
@@ -5817,7 +5816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>73</v>
       </c>
@@ -5854,7 +5853,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>74</v>
       </c>
@@ -5891,7 +5890,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>75</v>
       </c>
@@ -5928,7 +5927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -5963,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>77</v>
       </c>
@@ -6000,7 +5999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>78</v>
       </c>
@@ -6037,7 +6036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>79</v>
       </c>
@@ -6072,7 +6071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>80</v>
       </c>
@@ -6107,7 +6106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>81</v>
       </c>
@@ -6144,7 +6143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>82</v>
       </c>
@@ -6181,7 +6180,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>83</v>
       </c>
@@ -6218,7 +6217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>84</v>
       </c>
@@ -6255,7 +6254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>85</v>
       </c>
@@ -6292,7 +6291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>86</v>
       </c>
@@ -6329,7 +6328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>87</v>
       </c>
@@ -6364,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>88</v>
       </c>
@@ -6401,7 +6400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>89</v>
       </c>
@@ -6438,7 +6437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>90</v>
       </c>
@@ -6475,7 +6474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>91</v>
       </c>
@@ -6512,7 +6511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>92</v>
       </c>
@@ -6549,7 +6548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>93</v>
       </c>
@@ -6586,7 +6585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>94</v>
       </c>
@@ -6623,7 +6622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>95</v>
       </c>
@@ -6660,7 +6659,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>96</v>
       </c>
@@ -6697,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>97</v>
       </c>
@@ -6734,7 +6733,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>98</v>
       </c>
@@ -6771,7 +6770,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>99</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>100</v>
       </c>
@@ -6843,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>101</v>
       </c>
@@ -6880,7 +6879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>102</v>
       </c>
@@ -6915,7 +6914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>103</v>
       </c>
@@ -6952,7 +6951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>104</v>
       </c>
@@ -6987,7 +6986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>105</v>
       </c>
@@ -7024,7 +7023,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>106</v>
       </c>
@@ -7059,7 +7058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>107</v>
       </c>
@@ -7096,7 +7095,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>108</v>
       </c>
@@ -7133,7 +7132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>109</v>
       </c>
@@ -7170,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>110</v>
       </c>
@@ -7207,7 +7206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>111</v>
       </c>
@@ -7244,7 +7243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>112</v>
       </c>
@@ -7279,7 +7278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>113</v>
       </c>
@@ -7316,7 +7315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>114</v>
       </c>
@@ -7353,7 +7352,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>115</v>
       </c>
@@ -7390,7 +7389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>116</v>
       </c>
@@ -7425,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>117</v>
       </c>
@@ -7462,7 +7461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>118</v>
       </c>
@@ -7497,7 +7496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>119</v>
       </c>
@@ -7534,7 +7533,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>120</v>
       </c>
@@ -7571,7 +7570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>121</v>
       </c>
@@ -7606,7 +7605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>122</v>
       </c>
@@ -7643,7 +7642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>123</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>124</v>
       </c>
@@ -7717,7 +7716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>125</v>
       </c>
@@ -7752,7 +7751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>126</v>
       </c>
@@ -7789,7 +7788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>127</v>
       </c>
@@ -7826,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>128</v>
       </c>
@@ -7863,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>129</v>
       </c>
@@ -7900,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>130</v>
       </c>
@@ -7937,7 +7936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>131</v>
       </c>
@@ -7974,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>132</v>
       </c>
@@ -8011,7 +8010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>133</v>
       </c>
@@ -8048,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>134</v>
       </c>
@@ -8085,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>135</v>
       </c>
@@ -8122,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>136</v>
       </c>
@@ -8159,7 +8158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>137</v>
       </c>
@@ -8196,7 +8195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>138</v>
       </c>
@@ -8233,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>139</v>
       </c>
@@ -8270,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>140</v>
       </c>
@@ -8307,7 +8306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -8344,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>142</v>
       </c>
@@ -8381,7 +8380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>143</v>
       </c>
@@ -8418,7 +8417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>144</v>
       </c>
@@ -8455,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>145</v>
       </c>
@@ -8492,7 +8491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>146</v>
       </c>
@@ -8529,7 +8528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>147</v>
       </c>
@@ -8566,7 +8565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>148</v>
       </c>
@@ -8603,7 +8602,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>149</v>
       </c>
@@ -8640,7 +8639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>150</v>
       </c>
@@ -8677,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>151</v>
       </c>
@@ -8714,7 +8713,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>152</v>
       </c>
@@ -8751,7 +8750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>153</v>
       </c>
@@ -8788,7 +8787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>154</v>
       </c>
@@ -8823,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>155</v>
       </c>
@@ -8860,7 +8859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>156</v>
       </c>
@@ -8897,7 +8896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>157</v>
       </c>
@@ -8934,7 +8933,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>158</v>
       </c>
@@ -8971,7 +8970,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>159</v>
       </c>
@@ -9006,7 +9005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>160</v>
       </c>
@@ -9043,7 +9042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>161</v>
       </c>
@@ -9078,7 +9077,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>162</v>
       </c>
@@ -9115,7 +9114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>163</v>
       </c>
@@ -9152,7 +9151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>164</v>
       </c>
@@ -9187,7 +9186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>165</v>
       </c>
@@ -9224,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>166</v>
       </c>
@@ -9261,7 +9260,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>167</v>
       </c>
@@ -9298,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>168</v>
       </c>
@@ -9333,7 +9332,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>169</v>
       </c>
@@ -9368,7 +9367,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>170</v>
       </c>
@@ -9405,7 +9404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>171</v>
       </c>
@@ -9440,7 +9439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>172</v>
       </c>
@@ -9475,7 +9474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>173</v>
       </c>
@@ -9512,7 +9511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>174</v>
       </c>
@@ -9547,7 +9546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>175</v>
       </c>
@@ -9582,7 +9581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>176</v>
       </c>
@@ -9617,7 +9616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>177</v>
       </c>
@@ -9652,7 +9651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>178</v>
       </c>
@@ -9687,7 +9686,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>179</v>
       </c>
@@ -9724,7 +9723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>180</v>
       </c>
@@ -9759,7 +9758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>181</v>
       </c>
@@ -9794,7 +9793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>182</v>
       </c>
@@ -9831,7 +9830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>183</v>
       </c>
@@ -9868,7 +9867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>184</v>
       </c>
@@ -9905,7 +9904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>185</v>
       </c>
@@ -9942,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>186</v>
       </c>
@@ -9977,7 +9976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>187</v>
       </c>
@@ -10012,7 +10011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>188</v>
       </c>
@@ -10049,7 +10048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>189</v>
       </c>
@@ -10086,7 +10085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>190</v>
       </c>
@@ -10123,7 +10122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>191</v>
       </c>
@@ -10158,7 +10157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>192</v>
       </c>
@@ -10195,7 +10194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>193</v>
       </c>
@@ -10232,7 +10231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>194</v>
       </c>
@@ -10267,7 +10266,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>195</v>
       </c>
@@ -10302,7 +10301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>196</v>
       </c>
@@ -10337,7 +10336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>197</v>
       </c>
@@ -10372,7 +10371,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>198</v>
       </c>
@@ -10407,7 +10406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>199</v>
       </c>
@@ -10444,7 +10443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>200</v>
       </c>
@@ -10479,7 +10478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>201</v>
       </c>
@@ -10514,7 +10513,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>202</v>
       </c>
@@ -10549,7 +10548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>203</v>
       </c>
@@ -10584,7 +10583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>204</v>
       </c>
@@ -10621,7 +10620,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>205</v>
       </c>
@@ -10656,7 +10655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>206</v>
       </c>
@@ -10693,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>207</v>
       </c>
@@ -10728,7 +10727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>208</v>
       </c>
@@ -10763,7 +10762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>209</v>
       </c>
@@ -10800,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>210</v>
       </c>
@@ -10837,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>211</v>
       </c>
@@ -10874,7 +10873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>212</v>
       </c>
@@ -10911,7 +10910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>213</v>
       </c>
@@ -10946,7 +10945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>214</v>
       </c>
@@ -10981,7 +10980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>215</v>
       </c>
@@ -11016,7 +11015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>216</v>
       </c>
@@ -11051,7 +11050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>217</v>
       </c>
@@ -11086,7 +11085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>218</v>
       </c>
@@ -11121,7 +11120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>219</v>
       </c>
@@ -11161,13 +11160,6 @@
       <c r="B212" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O211" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="AM-S1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="50" priority="102"/>
   </conditionalFormatting>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48138569-E608-42B2-911B-A4F5C94C9E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C341E-7936-40A4-AD56-065AAA28A289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="WM" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AA!$A$1:$O$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AA!$A$1:$O$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WM!$A$1:$R$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="843">
   <si>
     <t>SKU</t>
   </si>
@@ -1394,9 +1394,6 @@
     <t>AI-03</t>
   </si>
   <si>
-    <t>AM-Mix4 OTG</t>
-  </si>
-  <si>
     <t>AA-22</t>
   </si>
   <si>
@@ -2469,13 +2466,115 @@
   </si>
   <si>
     <t>AM-W48 / AM-S6</t>
+  </si>
+  <si>
+    <t>BE-4T</t>
+  </si>
+  <si>
+    <t>FBA80128</t>
+  </si>
+  <si>
+    <t>B0H1H3K6B2</t>
+  </si>
+  <si>
+    <t>FBA80074</t>
+  </si>
+  <si>
+    <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+  </si>
+  <si>
+    <t>B0GY827J9C</t>
+  </si>
+  <si>
+    <t>FBA80075</t>
+  </si>
+  <si>
+    <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+  </si>
+  <si>
+    <t>B0GXPGBQB1</t>
+  </si>
+  <si>
+    <t>FBA80076</t>
+  </si>
+  <si>
+    <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+  </si>
+  <si>
+    <t>B0GY857139</t>
+  </si>
+  <si>
+    <t>FBA80077</t>
+  </si>
+  <si>
+    <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+  </si>
+  <si>
+    <t>B0GY86ZT1X</t>
+  </si>
+  <si>
+    <t>FBA80104</t>
+  </si>
+  <si>
+    <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+  </si>
+  <si>
+    <t>B0GXY7YJWP</t>
+  </si>
+  <si>
+    <t>FBA80105</t>
+  </si>
+  <si>
+    <t>UB-05 (AM-S2+AA-21)</t>
+  </si>
+  <si>
+    <t>B0H2FNV2RC</t>
+  </si>
+  <si>
+    <t>FBA80106</t>
+  </si>
+  <si>
+    <t>UB-06 (AM-S2+AA-22)</t>
+  </si>
+  <si>
+    <t>B0H2FCK54H</t>
+  </si>
+  <si>
+    <t>FBA80141</t>
+  </si>
+  <si>
+    <t>B0FJS57732</t>
+  </si>
+  <si>
+    <t>FBA80084</t>
+  </si>
+  <si>
+    <t>BE-4</t>
+  </si>
+  <si>
+    <t>B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>FBA80085</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>B0GXPBHDRF</t>
+  </si>
+  <si>
+    <t>FBA80143</t>
+  </si>
+  <si>
+    <t>B0H1MTP2ZP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2501,6 +2600,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2566,7 +2671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2598,6 +2703,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3425,7 +3533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
-  <dimension ref="A1:O212"/>
+  <dimension ref="A1:O223"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3458,19 +3566,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>607</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>608</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>5</v>
@@ -3488,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -3505,10 +3613,10 @@
         <v>409</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G2" s="2">
         <v>5000</v>
@@ -3552,10 +3660,10 @@
         <v>410</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -3589,10 +3697,10 @@
         <v>411</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -3623,13 +3731,13 @@
         <v>408</v>
       </c>
       <c r="D5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -3663,10 +3771,10 @@
         <v>412</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3700,10 +3808,10 @@
         <v>413</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3737,10 +3845,10 @@
         <v>414</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -3774,10 +3882,10 @@
         <v>415</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3811,10 +3919,10 @@
         <v>416</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3848,10 +3956,10 @@
         <v>417</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3885,10 +3993,10 @@
         <v>418</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -3922,10 +4030,10 @@
         <v>419</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -3959,10 +4067,10 @@
         <v>420</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -3996,10 +4104,10 @@
         <v>421</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -4033,10 +4141,10 @@
         <v>422</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -4070,10 +4178,10 @@
         <v>423</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -4107,10 +4215,10 @@
         <v>424</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -4145,7 +4253,7 @@
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -4179,10 +4287,10 @@
         <v>426</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -4216,10 +4324,10 @@
         <v>427</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -4253,10 +4361,10 @@
         <v>428</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -4290,10 +4398,10 @@
         <v>429</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -4328,7 +4436,7 @@
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -4362,10 +4470,10 @@
         <v>431</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -4399,10 +4507,10 @@
         <v>432</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4436,10 +4544,10 @@
         <v>433</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -4473,10 +4581,10 @@
         <v>434</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4511,7 +4619,7 @@
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4545,10 +4653,10 @@
         <v>436</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4583,7 +4691,7 @@
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4618,7 +4726,7 @@
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4652,10 +4760,10 @@
         <v>439</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4689,10 +4797,10 @@
         <v>440</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -4727,7 +4835,7 @@
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -4761,10 +4869,10 @@
         <v>442</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -4798,10 +4906,10 @@
         <v>443</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -4835,10 +4943,10 @@
         <v>444</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -4872,10 +4980,10 @@
         <v>445</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -4909,10 +5017,10 @@
         <v>446</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -4946,10 +5054,10 @@
         <v>447</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -4983,10 +5091,10 @@
         <v>448</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -5021,7 +5129,7 @@
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -5056,7 +5164,7 @@
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -5086,14 +5194,14 @@
       <c r="C45" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>451</v>
+      <c r="D45" s="12" t="s">
+        <v>809</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -5124,13 +5232,13 @@
         <v>408</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -5161,13 +5269,13 @@
         <v>408</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -5198,13 +5306,13 @@
         <v>408</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -5235,13 +5343,13 @@
         <v>408</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -5272,13 +5380,13 @@
         <v>408</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -5309,13 +5417,13 @@
         <v>408</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -5346,13 +5454,13 @@
         <v>408</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -5383,13 +5491,13 @@
         <v>408</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -5420,13 +5528,13 @@
         <v>408</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -5457,13 +5565,13 @@
         <v>408</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -5494,13 +5602,13 @@
         <v>408</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -5531,13 +5639,13 @@
         <v>408</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -5568,13 +5676,13 @@
         <v>408</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -5605,13 +5713,13 @@
         <v>408</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -5642,13 +5750,13 @@
         <v>408</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -5679,13 +5787,13 @@
         <v>408</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -5716,13 +5824,13 @@
         <v>408</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -5753,13 +5861,13 @@
         <v>408</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -5790,13 +5898,13 @@
         <v>408</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -5827,13 +5935,13 @@
         <v>408</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -5864,13 +5972,13 @@
         <v>408</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -5901,13 +6009,13 @@
         <v>408</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -5938,11 +6046,11 @@
         <v>408</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -5973,13 +6081,13 @@
         <v>408</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -6010,13 +6118,13 @@
         <v>408</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -6047,11 +6155,11 @@
         <v>408</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -6082,11 +6190,11 @@
         <v>408</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -6117,13 +6225,13 @@
         <v>408</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -6154,13 +6262,13 @@
         <v>408</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -6191,13 +6299,13 @@
         <v>408</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -6228,13 +6336,13 @@
         <v>408</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -6265,13 +6373,13 @@
         <v>408</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -6302,13 +6410,13 @@
         <v>408</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -6339,11 +6447,11 @@
         <v>408</v>
       </c>
       <c r="D79" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -6374,13 +6482,13 @@
         <v>408</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -6411,13 +6519,13 @@
         <v>408</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -6448,13 +6556,13 @@
         <v>408</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -6485,13 +6593,13 @@
         <v>408</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -6522,13 +6630,13 @@
         <v>408</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -6559,13 +6667,13 @@
         <v>408</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -6596,13 +6704,13 @@
         <v>408</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -6633,13 +6741,13 @@
         <v>408</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -6670,13 +6778,13 @@
         <v>408</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -6707,13 +6815,13 @@
         <v>408</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -6744,13 +6852,13 @@
         <v>408</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -6781,13 +6889,13 @@
         <v>408</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -6818,11 +6926,11 @@
         <v>408</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -6853,13 +6961,13 @@
         <v>408</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -6890,11 +6998,11 @@
         <v>408</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -6925,13 +7033,13 @@
         <v>408</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -6962,11 +7070,11 @@
         <v>408</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -6997,13 +7105,13 @@
         <v>408</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -7034,11 +7142,11 @@
         <v>408</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -7069,13 +7177,13 @@
         <v>408</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -7106,13 +7214,13 @@
         <v>408</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -7143,13 +7251,13 @@
         <v>408</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -7183,10 +7291,10 @@
         <v>431</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -7217,13 +7325,13 @@
         <v>408</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -7254,11 +7362,11 @@
         <v>408</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -7289,13 +7397,13 @@
         <v>408</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -7326,13 +7434,13 @@
         <v>408</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -7363,13 +7471,13 @@
         <v>408</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -7400,11 +7508,11 @@
         <v>408</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -7435,13 +7543,13 @@
         <v>408</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -7472,11 +7580,11 @@
         <v>408</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -7507,13 +7615,13 @@
         <v>408</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -7544,13 +7652,13 @@
         <v>408</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -7581,11 +7689,11 @@
         <v>408</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -7616,13 +7724,13 @@
         <v>408</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -7653,13 +7761,13 @@
         <v>408</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -7690,13 +7798,13 @@
         <v>408</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -7727,11 +7835,11 @@
         <v>408</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -7756,19 +7864,19 @@
         <v>126</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -7793,19 +7901,19 @@
         <v>127</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -7830,19 +7938,19 @@
         <v>128</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -7867,19 +7975,19 @@
         <v>129</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -7904,19 +8012,19 @@
         <v>130</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -7947,13 +8055,13 @@
         <v>408</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -7978,19 +8086,19 @@
         <v>132</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -8015,19 +8123,19 @@
         <v>133</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -8052,19 +8160,19 @@
         <v>134</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -8089,19 +8197,19 @@
         <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -8126,19 +8234,19 @@
         <v>136</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -8163,19 +8271,19 @@
         <v>137</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -8200,19 +8308,19 @@
         <v>138</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -8237,19 +8345,19 @@
         <v>139</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -8274,19 +8382,19 @@
         <v>140</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -8311,19 +8419,19 @@
         <v>141</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -8348,19 +8456,19 @@
         <v>142</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -8385,19 +8493,19 @@
         <v>143</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -8422,19 +8530,19 @@
         <v>144</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -8459,19 +8567,19 @@
         <v>145</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -8496,19 +8604,19 @@
         <v>146</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -8542,10 +8650,10 @@
         <v>410</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -8576,13 +8684,13 @@
         <v>408</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -8613,13 +8721,13 @@
         <v>408</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -8650,13 +8758,13 @@
         <v>408</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -8687,13 +8795,13 @@
         <v>408</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -8724,13 +8832,13 @@
         <v>408</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -8761,13 +8869,13 @@
         <v>408</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -8792,17 +8900,17 @@
         <v>154</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D146" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -8833,13 +8941,13 @@
         <v>408</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -8864,19 +8972,19 @@
         <v>156</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>408</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -8907,13 +9015,13 @@
         <v>408</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -8944,13 +9052,13 @@
         <v>408</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -8981,11 +9089,11 @@
         <v>408</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -9016,13 +9124,13 @@
         <v>408</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -9053,11 +9161,11 @@
         <v>408</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -9088,13 +9196,13 @@
         <v>408</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -9125,13 +9233,13 @@
         <v>408</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -9162,11 +9270,11 @@
         <v>408</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -9197,13 +9305,13 @@
         <v>408</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -9234,13 +9342,13 @@
         <v>408</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -9271,13 +9379,13 @@
         <v>408</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -9308,11 +9416,11 @@
         <v>408</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E160" s="4"/>
       <c r="F160" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -9343,11 +9451,11 @@
         <v>408</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E161" s="4"/>
       <c r="F161" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -9378,13 +9486,13 @@
         <v>408</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -9415,11 +9523,11 @@
         <v>408</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E163" s="4"/>
       <c r="F163" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -9450,11 +9558,11 @@
         <v>408</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E164" s="4"/>
       <c r="F164" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -9485,13 +9593,13 @@
         <v>408</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -9522,11 +9630,11 @@
         <v>408</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -9557,11 +9665,11 @@
         <v>408</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
@@ -9592,11 +9700,11 @@
         <v>408</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -9627,11 +9735,11 @@
         <v>408</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -9662,11 +9770,11 @@
         <v>408</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E170" s="4"/>
       <c r="F170" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
@@ -9697,13 +9805,13 @@
         <v>408</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -9734,11 +9842,11 @@
         <v>408</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -9769,11 +9877,11 @@
         <v>408</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
@@ -9804,13 +9912,13 @@
         <v>408</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
@@ -9841,13 +9949,13 @@
         <v>408</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -9878,13 +9986,13 @@
         <v>408</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -9915,13 +10023,13 @@
         <v>408</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -9952,11 +10060,11 @@
         <v>408</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -9987,11 +10095,11 @@
         <v>408</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E179" s="4"/>
       <c r="F179" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -10022,13 +10130,13 @@
         <v>408</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -10059,13 +10167,13 @@
         <v>408</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
@@ -10096,13 +10204,13 @@
         <v>408</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
@@ -10133,11 +10241,11 @@
         <v>408</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E183" s="4"/>
       <c r="F183" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
@@ -10168,13 +10276,13 @@
         <v>408</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
@@ -10205,13 +10313,13 @@
         <v>408</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
@@ -10242,11 +10350,11 @@
         <v>408</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E186" s="4"/>
       <c r="F186" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
@@ -10277,11 +10385,11 @@
         <v>408</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E187" s="4"/>
       <c r="F187" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
@@ -10312,11 +10420,11 @@
         <v>408</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
@@ -10347,11 +10455,11 @@
         <v>408</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E189" s="4"/>
       <c r="F189" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
@@ -10382,11 +10490,11 @@
         <v>408</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E190" s="4"/>
       <c r="F190" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
@@ -10417,13 +10525,13 @@
         <v>408</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
@@ -10454,11 +10562,11 @@
         <v>408</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
@@ -10489,11 +10597,11 @@
         <v>408</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E193" s="4"/>
       <c r="F193" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
@@ -10524,11 +10632,11 @@
         <v>408</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E194" s="4"/>
       <c r="F194" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
@@ -10559,11 +10667,11 @@
         <v>408</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -10594,13 +10702,13 @@
         <v>408</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -10631,11 +10739,11 @@
         <v>408</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -10666,13 +10774,13 @@
         <v>408</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -10703,11 +10811,11 @@
         <v>408</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
@@ -10738,11 +10846,11 @@
         <v>408</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -10773,13 +10881,13 @@
         <v>408</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -10810,13 +10918,13 @@
         <v>408</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -10847,13 +10955,13 @@
         <v>408</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -10884,13 +10992,13 @@
         <v>408</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -10921,11 +11029,11 @@
         <v>408</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -10956,11 +11064,11 @@
         <v>408</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
@@ -10991,11 +11099,11 @@
         <v>408</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -11026,11 +11134,11 @@
         <v>408</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
@@ -11061,11 +11169,11 @@
         <v>408</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
@@ -11096,11 +11204,11 @@
         <v>408</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
@@ -11131,11 +11239,11 @@
         <v>408</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
@@ -11156,10 +11264,247 @@
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A212" s="5"/>
-      <c r="B212" s="5"/>
+      <c r="A212" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B212" t="s">
+        <v>811</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>812</v>
+      </c>
+      <c r="B213" t="s">
+        <v>814</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D213" t="s">
+        <v>813</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>815</v>
+      </c>
+      <c r="B214" t="s">
+        <v>817</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D214" t="s">
+        <v>816</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>818</v>
+      </c>
+      <c r="B215" t="s">
+        <v>820</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D215" t="s">
+        <v>819</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I215" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>821</v>
+      </c>
+      <c r="B216" t="s">
+        <v>823</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D216" t="s">
+        <v>822</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>824</v>
+      </c>
+      <c r="B217" t="s">
+        <v>826</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D217" t="s">
+        <v>825</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I217" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>827</v>
+      </c>
+      <c r="B218" t="s">
+        <v>829</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D218" t="s">
+        <v>828</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I218" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>830</v>
+      </c>
+      <c r="B219" t="s">
+        <v>832</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D219" t="s">
+        <v>831</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I219" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>833</v>
+      </c>
+      <c r="B220" t="s">
+        <v>834</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D220" t="s">
+        <v>473</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I220" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>835</v>
+      </c>
+      <c r="B221" t="s">
+        <v>837</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D221" t="s">
+        <v>836</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I221" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>838</v>
+      </c>
+      <c r="B222" t="s">
+        <v>840</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D222" t="s">
+        <v>839</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I222" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>841</v>
+      </c>
+      <c r="B223" t="s">
+        <v>842</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D223" t="s">
+        <v>547</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I223" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O223" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}"/>
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="50" priority="102"/>
   </conditionalFormatting>
@@ -11197,19 +11542,19 @@
     <cfRule type="duplicateValues" dxfId="39" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="38" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A110">
-    <cfRule type="duplicateValues" dxfId="36" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A134">
     <cfRule type="duplicateValues" dxfId="34" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="33" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147:A155">
     <cfRule type="duplicateValues" dxfId="31" priority="122"/>
@@ -11218,7 +11563,7 @@
   <conditionalFormatting sqref="A156:A157">
     <cfRule type="duplicateValues" dxfId="29" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B212">
+  <conditionalFormatting sqref="A2:B211 A212 D212">
     <cfRule type="duplicateValues" dxfId="28" priority="129"/>
     <cfRule type="duplicateValues" dxfId="27" priority="130"/>
   </conditionalFormatting>
@@ -11259,8 +11604,8 @@
     <cfRule type="duplicateValues" dxfId="15" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="14" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="12" priority="69"/>
@@ -11313,22 +11658,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>756</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>613</v>
-      </c>
       <c r="H1" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>607</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>608</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>5</v>
@@ -11346,33 +11691,33 @@
         <v>9</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q1" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>761</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G2" s="2">
         <v>1000</v>
@@ -11405,33 +11750,33 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -11445,33 +11790,33 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -11485,33 +11830,33 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -11525,33 +11870,33 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -11565,33 +11910,33 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -11605,33 +11950,33 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -11645,33 +11990,33 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -11685,33 +12030,33 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R9" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -11725,33 +12070,33 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -11765,33 +12110,33 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -11805,33 +12150,33 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R12" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -11845,33 +12190,33 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -11885,33 +12230,33 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q14" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R14" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -11925,33 +12270,33 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -11965,33 +12310,33 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -12005,33 +12350,33 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -12045,33 +12390,33 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q18" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R18" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -12085,33 +12430,33 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q19" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R19" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -12125,33 +12470,33 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R20" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -12165,33 +12510,33 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q21" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R21" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -12205,33 +12550,33 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q22" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R22" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -12245,33 +12590,33 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q23" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R23" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -12285,33 +12630,33 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -12325,33 +12670,33 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="Q25" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="R25" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -12365,33 +12710,33 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q26" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R26" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -12405,33 +12750,33 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q27" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R27" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -12445,33 +12790,33 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -12485,33 +12830,33 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q29" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R29" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -12525,33 +12870,33 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q30" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R30" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -12565,33 +12910,33 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q31" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R31" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -12605,33 +12950,33 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R32" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -12645,33 +12990,33 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q33" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R33" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -12685,33 +13030,33 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q34" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R34" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -12725,33 +13070,33 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q35" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R35" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -12768,30 +13113,30 @@
         <v>9</v>
       </c>
       <c r="Q36" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R36" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -12808,30 +13153,30 @@
         <v>9</v>
       </c>
       <c r="Q37" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R37" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -12848,30 +13193,30 @@
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R38" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -12888,30 +13233,30 @@
         <v>9</v>
       </c>
       <c r="Q39" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R39" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -12928,30 +13273,30 @@
         <v>9</v>
       </c>
       <c r="Q40" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R40" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -12968,30 +13313,30 @@
         <v>9</v>
       </c>
       <c r="Q41" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R41" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B42" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -13008,30 +13353,30 @@
         <v>9</v>
       </c>
       <c r="Q42" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R42" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -13048,30 +13393,30 @@
         <v>9</v>
       </c>
       <c r="Q43" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R43" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -13085,33 +13430,33 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q44" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R44" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -13125,13 +13470,13 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q45" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R45" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897C341E-7936-40A4-AD56-065AAA28A289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41946D65-06A5-410B-909E-CDCAEA29C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="AA" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AA!$A$1:$O$223</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WM!$A$1:$R$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WM!$A$1:$R$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="842">
   <si>
     <t>SKU</t>
   </si>
@@ -2460,9 +2460,6 @@
   </si>
   <si>
     <t>AM-Pro8</t>
-  </si>
-  <si>
-    <t>AM-S1 Bookshelf Speaker</t>
   </si>
   <si>
     <t>AM-W48 / AM-S6</t>
@@ -3731,7 +3728,7 @@
         <v>408</v>
       </c>
       <c r="D5" t="s">
-        <v>807</v>
+        <v>411</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>766</v>
@@ -5195,7 +5192,7 @@
         <v>408</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>768</v>
@@ -8906,7 +8903,7 @@
         <v>408</v>
       </c>
       <c r="D146" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4" t="s">
@@ -11265,10 +11262,10 @@
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B212" t="s">
         <v>810</v>
-      </c>
-      <c r="B212" t="s">
-        <v>811</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>408</v>
@@ -11285,16 +11282,16 @@
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>811</v>
+      </c>
+      <c r="B213" t="s">
+        <v>813</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D213" t="s">
         <v>812</v>
-      </c>
-      <c r="B213" t="s">
-        <v>814</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D213" t="s">
-        <v>813</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>610</v>
@@ -11305,16 +11302,16 @@
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>814</v>
+      </c>
+      <c r="B214" t="s">
+        <v>816</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D214" t="s">
         <v>815</v>
-      </c>
-      <c r="B214" t="s">
-        <v>817</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D214" t="s">
-        <v>816</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>610</v>
@@ -11325,16 +11322,16 @@
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
+        <v>817</v>
+      </c>
+      <c r="B215" t="s">
+        <v>819</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D215" t="s">
         <v>818</v>
-      </c>
-      <c r="B215" t="s">
-        <v>820</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D215" t="s">
-        <v>819</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>610</v>
@@ -11345,16 +11342,16 @@
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
+        <v>820</v>
+      </c>
+      <c r="B216" t="s">
+        <v>822</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D216" t="s">
         <v>821</v>
-      </c>
-      <c r="B216" t="s">
-        <v>823</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D216" t="s">
-        <v>822</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>610</v>
@@ -11365,16 +11362,16 @@
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
+        <v>823</v>
+      </c>
+      <c r="B217" t="s">
+        <v>825</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D217" t="s">
         <v>824</v>
-      </c>
-      <c r="B217" t="s">
-        <v>826</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D217" t="s">
-        <v>825</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>610</v>
@@ -11385,16 +11382,16 @@
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
+        <v>826</v>
+      </c>
+      <c r="B218" t="s">
+        <v>828</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D218" t="s">
         <v>827</v>
-      </c>
-      <c r="B218" t="s">
-        <v>829</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D218" t="s">
-        <v>828</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>610</v>
@@ -11405,16 +11402,16 @@
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>829</v>
+      </c>
+      <c r="B219" t="s">
+        <v>831</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D219" t="s">
         <v>830</v>
-      </c>
-      <c r="B219" t="s">
-        <v>832</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D219" t="s">
-        <v>831</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>610</v>
@@ -11425,10 +11422,10 @@
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
+        <v>832</v>
+      </c>
+      <c r="B220" t="s">
         <v>833</v>
-      </c>
-      <c r="B220" t="s">
-        <v>834</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>408</v>
@@ -11445,16 +11442,16 @@
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
+        <v>834</v>
+      </c>
+      <c r="B221" t="s">
+        <v>836</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D221" t="s">
         <v>835</v>
-      </c>
-      <c r="B221" t="s">
-        <v>837</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D221" t="s">
-        <v>836</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>610</v>
@@ -11465,16 +11462,16 @@
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>837</v>
+      </c>
+      <c r="B222" t="s">
+        <v>839</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D222" t="s">
         <v>838</v>
-      </c>
-      <c r="B222" t="s">
-        <v>840</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D222" t="s">
-        <v>839</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>610</v>
@@ -11485,10 +11482,10 @@
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>840</v>
+      </c>
+      <c r="B223" t="s">
         <v>841</v>
-      </c>
-      <c r="B223" t="s">
-        <v>842</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>408</v>
@@ -11637,7 +11634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CFBFCC-8DAC-4EC0-9F68-2F31D96435DD}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -12321,13 +12318,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>669</v>
+        <v>629</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>670</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>739</v>
@@ -12361,13 +12358,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>739</v>
@@ -12401,13 +12398,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>739</v>
@@ -12441,13 +12438,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>739</v>
@@ -12481,13 +12478,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>739</v>
@@ -12521,19 +12518,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>739</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>756</v>
@@ -12561,19 +12558,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>739</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>756</v>
@@ -12601,22 +12598,22 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>756</v>
+        <v>610</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -12630,33 +12627,33 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Q24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>756</v>
+        <v>610</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -12670,33 +12667,33 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="Q25" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="R25" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>610</v>
+        <v>756</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -12721,22 +12718,22 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>610</v>
+        <v>756</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -12761,22 +12758,22 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>756</v>
+        <v>610</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -12801,22 +12798,22 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>756</v>
+        <v>610</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -12841,19 +12838,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>610</v>
@@ -12881,19 +12878,19 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>610</v>
@@ -12921,19 +12918,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>610</v>
@@ -12961,19 +12958,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>740</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>610</v>
@@ -13001,19 +12998,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>610</v>
@@ -13030,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>759</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="s">
         <v>762</v>
@@ -13041,19 +13038,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>610</v>
@@ -13070,7 +13067,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>759</v>
+        <v>9</v>
       </c>
       <c r="Q35" t="s">
         <v>762</v>
@@ -13081,13 +13078,13 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>751</v>
@@ -13107,7 +13104,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P36" t="s">
         <v>9</v>
@@ -13121,19 +13118,19 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>610</v>
@@ -13147,7 +13144,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P37" t="s">
         <v>9</v>
@@ -13161,19 +13158,19 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>610</v>
@@ -13187,7 +13184,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="P38" t="s">
         <v>9</v>
@@ -13201,13 +13198,13 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>752</v>
@@ -13227,7 +13224,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P39" t="s">
         <v>9</v>
@@ -13241,13 +13238,13 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>690</v>
+        <v>757</v>
+      </c>
+      <c r="B40" t="s">
+        <v>805</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>752</v>
@@ -13267,7 +13264,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="P40" t="s">
         <v>9</v>
@@ -13281,13 +13278,13 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>752</v>
@@ -13307,7 +13304,7 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="P41" t="s">
         <v>9</v>
@@ -13321,19 +13318,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="B42" t="s">
-        <v>805</v>
+        <v>652</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>693</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>610</v>
@@ -13347,10 +13344,10 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>9</v>
+        <v>759</v>
       </c>
       <c r="Q42" t="s">
         <v>762</v>
@@ -13361,19 +13358,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>610</v>
@@ -13387,10 +13384,10 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>9</v>
+        <v>759</v>
       </c>
       <c r="Q43" t="s">
         <v>762</v>
@@ -13399,97 +13396,18 @@
         <v>762</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2">
-        <v>1</v>
-      </c>
-      <c r="P44" t="s">
-        <v>759</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>762</v>
-      </c>
-      <c r="R44" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2">
-        <v>1</v>
-      </c>
-      <c r="P45" t="s">
-        <v>759</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>762</v>
-      </c>
-      <c r="R45" t="s">
-        <v>762</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:R43" xr:uid="{F0CFBFCC-8DAC-4EC0-9F68-2F31D96435DD}"/>
   <conditionalFormatting sqref="A13:A15">
     <cfRule type="duplicateValues" dxfId="4" priority="2"/>
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:A23">
+  <conditionalFormatting sqref="A20:A21">
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
     <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18:B45 B2:B15">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B17:B43 B2:B15">
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41946D65-06A5-410B-909E-CDCAEA29C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A72F9A0-4253-4F0D-B581-67E62C2F8BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="845">
   <si>
     <t>SKU</t>
   </si>
@@ -2565,6 +2565,15 @@
   </si>
   <si>
     <t>B0H1MTP2ZP</t>
+  </si>
+  <si>
+    <t>FBA79175</t>
+  </si>
+  <si>
+    <t>B0CPT2YJX2</t>
+  </si>
+  <si>
+    <t>WM-SMD09-WH</t>
   </si>
 </sst>
 </file>
@@ -2627,7 +2636,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2663,12 +2672,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2703,6 +2723,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11539,19 +11562,19 @@
     <cfRule type="duplicateValues" dxfId="39" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="38" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A110">
-    <cfRule type="duplicateValues" dxfId="36" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A134">
     <cfRule type="duplicateValues" dxfId="34" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="33" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147:A155">
     <cfRule type="duplicateValues" dxfId="31" priority="122"/>
@@ -11601,8 +11624,8 @@
     <cfRule type="duplicateValues" dxfId="15" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="14" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="12" priority="69"/>
@@ -11634,7 +11657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CFBFCC-8DAC-4EC0-9F68-2F31D96435DD}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -13394,6 +13417,38 @@
       </c>
       <c r="R43" t="s">
         <v>762</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>842</v>
+      </c>
+      <c r="B44" t="s">
+        <v>843</v>
+      </c>
+      <c r="C44" t="s">
+        <v>844</v>
+      </c>
+      <c r="D44" t="s">
+        <v>739</v>
+      </c>
+      <c r="E44" t="s">
+        <v>742</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="O44" s="13">
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>763</v>
+      </c>
+      <c r="R44" t="s">
+        <v>763</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A72F9A0-4253-4F0D-B581-67E62C2F8BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2476F9D6-173C-4C5E-9AFB-64CF57A0789A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
   <sheets>
     <sheet name="AA" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="935">
   <si>
     <t>SKU</t>
   </si>
@@ -2574,6 +2574,276 @@
   </si>
   <si>
     <t>WM-SMD09-WH</t>
+  </si>
+  <si>
+    <t>FBA80006</t>
+  </si>
+  <si>
+    <t>FBA76731</t>
+  </si>
+  <si>
+    <t>FBA76713</t>
+  </si>
+  <si>
+    <t>FBA76709</t>
+  </si>
+  <si>
+    <t>FBA76710</t>
+  </si>
+  <si>
+    <t>FBA76711</t>
+  </si>
+  <si>
+    <t>FBA76712</t>
+  </si>
+  <si>
+    <t>FBA76714</t>
+  </si>
+  <si>
+    <t>FBA79006</t>
+  </si>
+  <si>
+    <t>FBA79007</t>
+  </si>
+  <si>
+    <t>FBA79326</t>
+  </si>
+  <si>
+    <t>FBA79327</t>
+  </si>
+  <si>
+    <t>FBA79328</t>
+  </si>
+  <si>
+    <t>FBA79329</t>
+  </si>
+  <si>
+    <t>FBA80109</t>
+  </si>
+  <si>
+    <t>FBA80110</t>
+  </si>
+  <si>
+    <t>FBA80119</t>
+  </si>
+  <si>
+    <t>FBA80120</t>
+  </si>
+  <si>
+    <t>FBA80121</t>
+  </si>
+  <si>
+    <t>FBA80122</t>
+  </si>
+  <si>
+    <t>FBA80123</t>
+  </si>
+  <si>
+    <t>FBA80124</t>
+  </si>
+  <si>
+    <t>FBA80125</t>
+  </si>
+  <si>
+    <t>FBA80126</t>
+  </si>
+  <si>
+    <t>FBA80129</t>
+  </si>
+  <si>
+    <t>FBA80130</t>
+  </si>
+  <si>
+    <t>FBA80131</t>
+  </si>
+  <si>
+    <t>FBA80132</t>
+  </si>
+  <si>
+    <t>FBA80133</t>
+  </si>
+  <si>
+    <t>FBA80134</t>
+  </si>
+  <si>
+    <t>FBA80135</t>
+  </si>
+  <si>
+    <t>FBA80136</t>
+  </si>
+  <si>
+    <t>FBA80137</t>
+  </si>
+  <si>
+    <t>FBA80138</t>
+  </si>
+  <si>
+    <t>FBA80142</t>
+  </si>
+  <si>
+    <t>FBA80114</t>
+  </si>
+  <si>
+    <t>FBA80115</t>
+  </si>
+  <si>
+    <t>FBA80116</t>
+  </si>
+  <si>
+    <t>FBA80117</t>
+  </si>
+  <si>
+    <t>ASIN Not created</t>
+  </si>
+  <si>
+    <t>B0BLK9QL7X</t>
+  </si>
+  <si>
+    <t>B0BLK1Z7PJ</t>
+  </si>
+  <si>
+    <t>B0BLJYX15C</t>
+  </si>
+  <si>
+    <t>B0CYLXLBRL</t>
+  </si>
+  <si>
+    <t>B0CYLVB618</t>
+  </si>
+  <si>
+    <t>B0CYLXL5GY</t>
+  </si>
+  <si>
+    <t>B0CYLXC8BQ</t>
+  </si>
+  <si>
+    <t>B0H2ZCQFTZ</t>
+  </si>
+  <si>
+    <t>B0H2Z6R6V8</t>
+  </si>
+  <si>
+    <t>B0H3LHF2WW</t>
+  </si>
+  <si>
+    <t>A2-XLR</t>
+  </si>
+  <si>
+    <t>AM-W48</t>
+  </si>
+  <si>
+    <t>AM-W44</t>
+  </si>
+  <si>
+    <t>AM-W42</t>
+  </si>
+  <si>
+    <t>AM-W38</t>
+  </si>
+  <si>
+    <t>AM-W39</t>
+  </si>
+  <si>
+    <t>AM-W40</t>
+  </si>
+  <si>
+    <t>AM-W41</t>
+  </si>
+  <si>
+    <t>AM-W43</t>
+  </si>
+  <si>
+    <t>AK-S1</t>
+  </si>
+  <si>
+    <t>AK-S2</t>
+  </si>
+  <si>
+    <t>AB-06</t>
+  </si>
+  <si>
+    <t>AB-07</t>
+  </si>
+  <si>
+    <t>AB-08</t>
+  </si>
+  <si>
+    <t>AB-09</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>AM-C53</t>
+  </si>
+  <si>
+    <t>AM-C54</t>
+  </si>
+  <si>
+    <t>AM-C55</t>
+  </si>
+  <si>
+    <t>AM-C56</t>
+  </si>
+  <si>
+    <t>AM-W25</t>
+  </si>
+  <si>
+    <t>AA-26 Pro</t>
+  </si>
+  <si>
+    <t>AA-27</t>
+  </si>
+  <si>
+    <t>AA-28</t>
+  </si>
+  <si>
+    <t>HP4</t>
+  </si>
+  <si>
+    <t>HPA1400</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>PRE103</t>
+  </si>
+  <si>
+    <t>DI20</t>
+  </si>
+  <si>
+    <t>AC1</t>
+  </si>
+  <si>
+    <t>IS-2</t>
+  </si>
+  <si>
+    <t>IS-3</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>MS155</t>
+  </si>
+  <si>
+    <t>AM-C5 White</t>
+  </si>
+  <si>
+    <t>AH-53</t>
+  </si>
+  <si>
+    <t>AH-50-DH</t>
+  </si>
+  <si>
+    <t>AH-40 Pro</t>
+  </si>
+  <si>
+    <t>AH-53 Pro</t>
   </si>
 </sst>
 </file>
@@ -2688,7 +2958,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2724,9 +2994,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3553,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98773489-E591-4874-A9C1-F7B78C71D228}">
-  <dimension ref="A1:O223"/>
+  <dimension ref="A1:O263"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -11302,6 +11573,9 @@
       <c r="I212" s="2">
         <v>0</v>
       </c>
+      <c r="O212" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
@@ -11322,6 +11596,9 @@
       <c r="I213" s="2">
         <v>0</v>
       </c>
+      <c r="O213" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
@@ -11342,6 +11619,9 @@
       <c r="I214" s="2">
         <v>0</v>
       </c>
+      <c r="O214" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
@@ -11362,6 +11642,9 @@
       <c r="I215" s="2">
         <v>0</v>
       </c>
+      <c r="O215" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
@@ -11382,6 +11665,9 @@
       <c r="I216" s="2">
         <v>0</v>
       </c>
+      <c r="O216" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
@@ -11402,6 +11688,9 @@
       <c r="I217" s="2">
         <v>0</v>
       </c>
+      <c r="O217" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
@@ -11422,6 +11711,9 @@
       <c r="I218" s="2">
         <v>0</v>
       </c>
+      <c r="O218" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
@@ -11442,6 +11734,9 @@
       <c r="I219" s="2">
         <v>0</v>
       </c>
+      <c r="O219" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
@@ -11462,6 +11757,9 @@
       <c r="I220" s="2">
         <v>0</v>
       </c>
+      <c r="O220" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
@@ -11482,6 +11780,9 @@
       <c r="I221" s="2">
         <v>0</v>
       </c>
+      <c r="O221" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
@@ -11502,6 +11803,9 @@
       <c r="I222" s="2">
         <v>0</v>
       </c>
+      <c r="O222" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
@@ -11520,6 +11824,809 @@
         <v>610</v>
       </c>
       <c r="I223" s="2">
+        <v>0</v>
+      </c>
+      <c r="O223" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>845</v>
+      </c>
+      <c r="B224" t="s">
+        <v>884</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D224" t="s">
+        <v>895</v>
+      </c>
+      <c r="F224" t="s">
+        <v>610</v>
+      </c>
+      <c r="O224" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>154</v>
+      </c>
+      <c r="B225" t="s">
+        <v>605</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D225" t="s">
+        <v>896</v>
+      </c>
+      <c r="F225" t="s">
+        <v>610</v>
+      </c>
+      <c r="O225" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>846</v>
+      </c>
+      <c r="B226" t="s">
+        <v>885</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D226" t="s">
+        <v>897</v>
+      </c>
+      <c r="F226" t="s">
+        <v>610</v>
+      </c>
+      <c r="O226" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>847</v>
+      </c>
+      <c r="B227" t="s">
+        <v>886</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D227" t="s">
+        <v>898</v>
+      </c>
+      <c r="F227" t="s">
+        <v>610</v>
+      </c>
+      <c r="O227" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>848</v>
+      </c>
+      <c r="B228" t="s">
+        <v>887</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D228" t="s">
+        <v>899</v>
+      </c>
+      <c r="F228" t="s">
+        <v>610</v>
+      </c>
+      <c r="O228" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>849</v>
+      </c>
+      <c r="B229" t="s">
+        <v>884</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D229" t="s">
+        <v>900</v>
+      </c>
+      <c r="F229" t="s">
+        <v>610</v>
+      </c>
+      <c r="O229" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>850</v>
+      </c>
+      <c r="B230" t="s">
+        <v>884</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D230" t="s">
+        <v>901</v>
+      </c>
+      <c r="F230" t="s">
+        <v>610</v>
+      </c>
+      <c r="O230" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>851</v>
+      </c>
+      <c r="B231" t="s">
+        <v>884</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D231" t="s">
+        <v>902</v>
+      </c>
+      <c r="F231" t="s">
+        <v>610</v>
+      </c>
+      <c r="O231" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>852</v>
+      </c>
+      <c r="B232" t="s">
+        <v>884</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D232" t="s">
+        <v>903</v>
+      </c>
+      <c r="F232" t="s">
+        <v>610</v>
+      </c>
+      <c r="O232" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>853</v>
+      </c>
+      <c r="B233" t="s">
+        <v>884</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D233" t="s">
+        <v>904</v>
+      </c>
+      <c r="F233" t="s">
+        <v>610</v>
+      </c>
+      <c r="O233" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>854</v>
+      </c>
+      <c r="B234" t="s">
+        <v>884</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D234" t="s">
+        <v>905</v>
+      </c>
+      <c r="F234" t="s">
+        <v>610</v>
+      </c>
+      <c r="O234" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>855</v>
+      </c>
+      <c r="B235" t="s">
+        <v>888</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D235" t="s">
+        <v>906</v>
+      </c>
+      <c r="F235" t="s">
+        <v>610</v>
+      </c>
+      <c r="O235" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>856</v>
+      </c>
+      <c r="B236" t="s">
+        <v>889</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D236" t="s">
+        <v>907</v>
+      </c>
+      <c r="F236" t="s">
+        <v>610</v>
+      </c>
+      <c r="O236" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>857</v>
+      </c>
+      <c r="B237" t="s">
+        <v>890</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D237" t="s">
+        <v>908</v>
+      </c>
+      <c r="F237" t="s">
+        <v>610</v>
+      </c>
+      <c r="O237" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>858</v>
+      </c>
+      <c r="B238" t="s">
+        <v>891</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D238" t="s">
+        <v>909</v>
+      </c>
+      <c r="F238" t="s">
+        <v>610</v>
+      </c>
+      <c r="O238" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>859</v>
+      </c>
+      <c r="B239" t="s">
+        <v>892</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D239" t="s">
+        <v>910</v>
+      </c>
+      <c r="F239" t="s">
+        <v>610</v>
+      </c>
+      <c r="O239" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>860</v>
+      </c>
+      <c r="B240" t="s">
+        <v>893</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D240" t="s">
+        <v>911</v>
+      </c>
+      <c r="F240" t="s">
+        <v>610</v>
+      </c>
+      <c r="O240" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>861</v>
+      </c>
+      <c r="B241" t="s">
+        <v>884</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D241" t="s">
+        <v>912</v>
+      </c>
+      <c r="F241" t="s">
+        <v>610</v>
+      </c>
+      <c r="O241" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>862</v>
+      </c>
+      <c r="B242" t="s">
+        <v>884</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D242" t="s">
+        <v>913</v>
+      </c>
+      <c r="F242" t="s">
+        <v>610</v>
+      </c>
+      <c r="O242" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>863</v>
+      </c>
+      <c r="B243" t="s">
+        <v>884</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D243" t="s">
+        <v>914</v>
+      </c>
+      <c r="F243" t="s">
+        <v>610</v>
+      </c>
+      <c r="O243" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>864</v>
+      </c>
+      <c r="B244" t="s">
+        <v>884</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D244" t="s">
+        <v>915</v>
+      </c>
+      <c r="F244" t="s">
+        <v>610</v>
+      </c>
+      <c r="O244" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>865</v>
+      </c>
+      <c r="B245" t="s">
+        <v>884</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D245" t="s">
+        <v>916</v>
+      </c>
+      <c r="F245" t="s">
+        <v>610</v>
+      </c>
+      <c r="O245" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>866</v>
+      </c>
+      <c r="B246" t="s">
+        <v>884</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D246" t="s">
+        <v>917</v>
+      </c>
+      <c r="F246" t="s">
+        <v>610</v>
+      </c>
+      <c r="O246" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>867</v>
+      </c>
+      <c r="B247" t="s">
+        <v>884</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D247" t="s">
+        <v>918</v>
+      </c>
+      <c r="F247" t="s">
+        <v>610</v>
+      </c>
+      <c r="O247" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>868</v>
+      </c>
+      <c r="B248" t="s">
+        <v>884</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D248" t="s">
+        <v>919</v>
+      </c>
+      <c r="F248" t="s">
+        <v>610</v>
+      </c>
+      <c r="O248" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>869</v>
+      </c>
+      <c r="B249" t="s">
+        <v>884</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D249" t="s">
+        <v>920</v>
+      </c>
+      <c r="F249" t="s">
+        <v>610</v>
+      </c>
+      <c r="O249" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>870</v>
+      </c>
+      <c r="B250" t="s">
+        <v>884</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D250" t="s">
+        <v>921</v>
+      </c>
+      <c r="F250" t="s">
+        <v>610</v>
+      </c>
+      <c r="O250" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>871</v>
+      </c>
+      <c r="B251" t="s">
+        <v>884</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D251" t="s">
+        <v>922</v>
+      </c>
+      <c r="F251" t="s">
+        <v>610</v>
+      </c>
+      <c r="O251" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>872</v>
+      </c>
+      <c r="B252" t="s">
+        <v>884</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D252" t="s">
+        <v>923</v>
+      </c>
+      <c r="F252" t="s">
+        <v>610</v>
+      </c>
+      <c r="O252" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>873</v>
+      </c>
+      <c r="B253" t="s">
+        <v>884</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D253" t="s">
+        <v>924</v>
+      </c>
+      <c r="F253" t="s">
+        <v>610</v>
+      </c>
+      <c r="O253" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>874</v>
+      </c>
+      <c r="B254" t="s">
+        <v>884</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D254" t="s">
+        <v>925</v>
+      </c>
+      <c r="F254" t="s">
+        <v>610</v>
+      </c>
+      <c r="O254" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>875</v>
+      </c>
+      <c r="B255" t="s">
+        <v>884</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D255" t="s">
+        <v>926</v>
+      </c>
+      <c r="F255" t="s">
+        <v>610</v>
+      </c>
+      <c r="O255" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>876</v>
+      </c>
+      <c r="B256" t="s">
+        <v>884</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D256" t="s">
+        <v>927</v>
+      </c>
+      <c r="F256" t="s">
+        <v>610</v>
+      </c>
+      <c r="O256" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>877</v>
+      </c>
+      <c r="B257" t="s">
+        <v>884</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D257" t="s">
+        <v>928</v>
+      </c>
+      <c r="F257" t="s">
+        <v>610</v>
+      </c>
+      <c r="O257" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>878</v>
+      </c>
+      <c r="B258" t="s">
+        <v>884</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D258" t="s">
+        <v>929</v>
+      </c>
+      <c r="F258" t="s">
+        <v>610</v>
+      </c>
+      <c r="O258" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>879</v>
+      </c>
+      <c r="B259" t="s">
+        <v>894</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D259" t="s">
+        <v>930</v>
+      </c>
+      <c r="F259" t="s">
+        <v>610</v>
+      </c>
+      <c r="O259" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>880</v>
+      </c>
+      <c r="B260" t="s">
+        <v>884</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D260" t="s">
+        <v>931</v>
+      </c>
+      <c r="F260" t="s">
+        <v>610</v>
+      </c>
+      <c r="O260" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>881</v>
+      </c>
+      <c r="B261" t="s">
+        <v>884</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D261" t="s">
+        <v>932</v>
+      </c>
+      <c r="F261" t="s">
+        <v>610</v>
+      </c>
+      <c r="O261" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>882</v>
+      </c>
+      <c r="B262" t="s">
+        <v>884</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D262" t="s">
+        <v>933</v>
+      </c>
+      <c r="F262" t="s">
+        <v>610</v>
+      </c>
+      <c r="O262" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>883</v>
+      </c>
+      <c r="B263" t="s">
+        <v>884</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D263" t="s">
+        <v>934</v>
+      </c>
+      <c r="F263" t="s">
+        <v>610</v>
+      </c>
+      <c r="O263" s="14">
         <v>0</v>
       </c>
     </row>
@@ -11562,19 +12669,19 @@
     <cfRule type="duplicateValues" dxfId="39" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="38" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A110">
-    <cfRule type="duplicateValues" dxfId="36" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A134">
     <cfRule type="duplicateValues" dxfId="34" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="33" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147:A155">
     <cfRule type="duplicateValues" dxfId="31" priority="122"/>
@@ -11624,8 +12731,8 @@
     <cfRule type="duplicateValues" dxfId="15" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="14" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="12" priority="69"/>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2476F9D6-173C-4C5E-9AFB-64CF57A0789A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EDE032-9C0E-4D71-8A62-37C06DB890BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E071ED51-FC72-421D-856E-2A4DF68E7BC3}"/>
   </bookViews>
@@ -2997,7 +2997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12669,19 +12669,19 @@
     <cfRule type="duplicateValues" dxfId="39" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="38" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A108:A110">
-    <cfRule type="duplicateValues" dxfId="36" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A112:A134">
     <cfRule type="duplicateValues" dxfId="34" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A138">
-    <cfRule type="duplicateValues" dxfId="33" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A147:A155">
     <cfRule type="duplicateValues" dxfId="31" priority="122"/>
@@ -12731,8 +12731,8 @@
     <cfRule type="duplicateValues" dxfId="15" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="14" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="12" priority="69"/>

--- a/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
+++ b/data/input/Audio Array & WM Replenishment/AA & WM Replenishment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\Audio Array &amp; WM Replenishment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5274601D-D27C-4F8C-A90E-E33561C06E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14286BA9-210E-4C59-BAA3-BA95F22A1B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="1032">
   <si>
     <t>SKU</t>
   </si>
@@ -2850,13 +2850,295 @@
   </si>
   <si>
     <t>WM-SMD09-WH</t>
+  </si>
+  <si>
+    <t>FBA77101</t>
+  </si>
+  <si>
+    <t>B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>Tonor</t>
+  </si>
+  <si>
+    <t>TC-777</t>
+  </si>
+  <si>
+    <t>FBA77104</t>
+  </si>
+  <si>
+    <t>B089SJGQBH</t>
+  </si>
+  <si>
+    <t>TC20</t>
+  </si>
+  <si>
+    <t>FBA77111</t>
+  </si>
+  <si>
+    <t>B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>TC30</t>
+  </si>
+  <si>
+    <t>FBA79113</t>
+  </si>
+  <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>TC310</t>
+  </si>
+  <si>
+    <t>FBA79114</t>
+  </si>
+  <si>
+    <t>B0CCV74CL7</t>
+  </si>
+  <si>
+    <t>TC310+</t>
+  </si>
+  <si>
+    <t>FBA79116</t>
+  </si>
+  <si>
+    <t>B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>TC-777 PRO</t>
+  </si>
+  <si>
+    <t>FBA77113</t>
+  </si>
+  <si>
+    <t>B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>FBA79111</t>
+  </si>
+  <si>
+    <t>B0BRKFP94K</t>
+  </si>
+  <si>
+    <t>TD510</t>
+  </si>
+  <si>
+    <t>FBA77110</t>
+  </si>
+  <si>
+    <t>B08NDB5NWP</t>
+  </si>
+  <si>
+    <t>TM20</t>
+  </si>
+  <si>
+    <t>Conference Microphone</t>
+  </si>
+  <si>
+    <t>FBK77102</t>
+  </si>
+  <si>
+    <t>B07GVGMW59</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>FBA77117</t>
+  </si>
+  <si>
+    <t>B078WNW4YW</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>FBA79115</t>
+  </si>
+  <si>
+    <t>B0C8JDHLX9</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>FBA77106</t>
+  </si>
+  <si>
+    <t>B082W4B7SX</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>FBA77105</t>
+  </si>
+  <si>
+    <t>B089FVQD3Z</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>Non IXD</t>
+  </si>
+  <si>
+    <t>FBA79112</t>
+  </si>
+  <si>
+    <t>B0BRKDLXCD</t>
+  </si>
+  <si>
+    <t>T90</t>
+  </si>
+  <si>
+    <t>FBA77103</t>
+  </si>
+  <si>
+    <t>B09Z5Q194D</t>
+  </si>
+  <si>
+    <t>ORCA001</t>
+  </si>
+  <si>
+    <t>FBA77114</t>
+  </si>
+  <si>
+    <t>B07TSN2H9D</t>
+  </si>
+  <si>
+    <t>TC-2030</t>
+  </si>
+  <si>
+    <t>FBA79574</t>
+  </si>
+  <si>
+    <t>B0B4WTHLX5</t>
+  </si>
+  <si>
+    <t>TC30S</t>
+  </si>
+  <si>
+    <t>FBA79575</t>
+  </si>
+  <si>
+    <t>B0BG8CJXHH</t>
+  </si>
+  <si>
+    <t>TC30+</t>
+  </si>
+  <si>
+    <t>FBA79576</t>
+  </si>
+  <si>
+    <t>B0BRCR2QQ7</t>
+  </si>
+  <si>
+    <t>TC30S+</t>
+  </si>
+  <si>
+    <t>FBA79577</t>
+  </si>
+  <si>
+    <t>B0CSCT63BL</t>
+  </si>
+  <si>
+    <t>TM310</t>
+  </si>
+  <si>
+    <t>FBA79578</t>
+  </si>
+  <si>
+    <t>B0CFKZ72N7</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>FBA79579</t>
+  </si>
+  <si>
+    <t>B0CQX4GVSB</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>FBA79582</t>
+  </si>
+  <si>
+    <t>B0CCVBQRFX</t>
+  </si>
+  <si>
+    <t>TD510+</t>
+  </si>
+  <si>
+    <t>FBA79585</t>
+  </si>
+  <si>
+    <t>B0CFKHCQ8W</t>
+  </si>
+  <si>
+    <t>T20LP</t>
+  </si>
+  <si>
+    <t>FBA79586</t>
+  </si>
+  <si>
+    <t>B0CH9JR3HL</t>
+  </si>
+  <si>
+    <t>TRL-20</t>
+  </si>
+  <si>
+    <t>FBA79697</t>
+  </si>
+  <si>
+    <t>B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>TD310</t>
+  </si>
+  <si>
+    <t>FBA79696</t>
+  </si>
+  <si>
+    <t>B0CQX3VB1R</t>
+  </si>
+  <si>
+    <t>TD310+</t>
+  </si>
+  <si>
+    <t>FBA77115</t>
+  </si>
+  <si>
+    <t>B08V1JS3NY</t>
+  </si>
+  <si>
+    <t>TC40</t>
+  </si>
+  <si>
+    <t>FBA77116</t>
+  </si>
+  <si>
+    <t>B0BBL47VR5</t>
+  </si>
+  <si>
+    <t>TC40 RGB</t>
+  </si>
+  <si>
+    <t>FBM79585</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2891,8 +3173,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2908,6 +3197,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2964,7 +3259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3004,6 +3299,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3830,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P263"/>
+  <dimension ref="A1:P294"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -13424,6 +13731,998 @@
       <c r="P263" s="14">
         <v>0</v>
       </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A264" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="B264" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="C264" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D264" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="E264" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G264" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H264" s="16"/>
+      <c r="I264" s="16"/>
+      <c r="J264" s="16"/>
+      <c r="K264" s="16"/>
+      <c r="L264" s="16"/>
+      <c r="M264" s="16"/>
+      <c r="N264" s="16"/>
+      <c r="O264" s="16"/>
+      <c r="P264" s="16"/>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A265" s="15" t="s">
+        <v>942</v>
+      </c>
+      <c r="B265" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="C265" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D265" s="15" t="s">
+        <v>944</v>
+      </c>
+      <c r="E265" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G265" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H265" s="16"/>
+      <c r="I265" s="16"/>
+      <c r="J265" s="16"/>
+      <c r="K265" s="16"/>
+      <c r="L265" s="16"/>
+      <c r="M265" s="16"/>
+      <c r="N265" s="16"/>
+      <c r="O265" s="16"/>
+      <c r="P265" s="16"/>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A266" s="15" t="s">
+        <v>945</v>
+      </c>
+      <c r="B266" s="15" t="s">
+        <v>946</v>
+      </c>
+      <c r="C266" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D266" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="E266" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G266" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H266" s="16"/>
+      <c r="I266" s="16"/>
+      <c r="J266" s="16"/>
+      <c r="K266" s="16"/>
+      <c r="L266" s="16"/>
+      <c r="M266" s="16"/>
+      <c r="N266" s="16"/>
+      <c r="O266" s="16"/>
+      <c r="P266" s="16"/>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A267" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="B267" s="15" t="s">
+        <v>949</v>
+      </c>
+      <c r="C267" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D267" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="E267" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G267" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H267" s="16"/>
+      <c r="I267" s="16"/>
+      <c r="J267" s="16"/>
+      <c r="K267" s="16"/>
+      <c r="L267" s="16"/>
+      <c r="M267" s="16"/>
+      <c r="N267" s="16"/>
+      <c r="O267" s="16"/>
+      <c r="P267" s="16"/>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A268" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="B268" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="C268" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D268" s="15" t="s">
+        <v>953</v>
+      </c>
+      <c r="E268" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G268" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H268" s="16"/>
+      <c r="I268" s="16"/>
+      <c r="J268" s="16"/>
+      <c r="K268" s="16"/>
+      <c r="L268" s="16"/>
+      <c r="M268" s="16"/>
+      <c r="N268" s="16"/>
+      <c r="O268" s="16"/>
+      <c r="P268" s="16"/>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A269" s="15" t="s">
+        <v>954</v>
+      </c>
+      <c r="B269" s="15" t="s">
+        <v>955</v>
+      </c>
+      <c r="C269" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D269" s="15" t="s">
+        <v>956</v>
+      </c>
+      <c r="E269" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G269" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H269" s="16"/>
+      <c r="I269" s="16"/>
+      <c r="J269" s="16"/>
+      <c r="K269" s="16"/>
+      <c r="L269" s="16"/>
+      <c r="M269" s="16"/>
+      <c r="N269" s="16"/>
+      <c r="O269" s="16"/>
+      <c r="P269" s="16"/>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A270" s="15" t="s">
+        <v>957</v>
+      </c>
+      <c r="B270" s="15" t="s">
+        <v>958</v>
+      </c>
+      <c r="C270" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D270" s="15" t="s">
+        <v>959</v>
+      </c>
+      <c r="E270" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G270" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H270" s="16"/>
+      <c r="I270" s="16"/>
+      <c r="J270" s="16"/>
+      <c r="K270" s="16"/>
+      <c r="L270" s="16"/>
+      <c r="M270" s="16"/>
+      <c r="N270" s="16"/>
+      <c r="O270" s="16"/>
+      <c r="P270" s="16"/>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A271" s="15" t="s">
+        <v>960</v>
+      </c>
+      <c r="B271" s="15" t="s">
+        <v>961</v>
+      </c>
+      <c r="C271" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D271" s="15" t="s">
+        <v>962</v>
+      </c>
+      <c r="E271" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G271" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H271" s="16"/>
+      <c r="I271" s="16"/>
+      <c r="J271" s="16"/>
+      <c r="K271" s="16"/>
+      <c r="L271" s="16"/>
+      <c r="M271" s="16"/>
+      <c r="N271" s="16"/>
+      <c r="O271" s="16"/>
+      <c r="P271" s="16"/>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A272" s="15" t="s">
+        <v>963</v>
+      </c>
+      <c r="B272" s="15" t="s">
+        <v>964</v>
+      </c>
+      <c r="C272" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D272" s="15" t="s">
+        <v>965</v>
+      </c>
+      <c r="E272" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G272" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H272" s="16"/>
+      <c r="I272" s="16"/>
+      <c r="J272" s="16"/>
+      <c r="K272" s="16"/>
+      <c r="L272" s="16"/>
+      <c r="M272" s="16"/>
+      <c r="N272" s="16"/>
+      <c r="O272" s="16"/>
+      <c r="P272" s="16"/>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A273" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="B273" s="15" t="s">
+        <v>968</v>
+      </c>
+      <c r="C273" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D273" s="15" t="s">
+        <v>969</v>
+      </c>
+      <c r="E273" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G273" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H273" s="16"/>
+      <c r="I273" s="16"/>
+      <c r="J273" s="16"/>
+      <c r="K273" s="16"/>
+      <c r="L273" s="16"/>
+      <c r="M273" s="16"/>
+      <c r="N273" s="16"/>
+      <c r="O273" s="16"/>
+      <c r="P273" s="16"/>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A274" s="15" t="s">
+        <v>970</v>
+      </c>
+      <c r="B274" s="15" t="s">
+        <v>971</v>
+      </c>
+      <c r="C274" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D274" s="15" t="s">
+        <v>972</v>
+      </c>
+      <c r="E274" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G274" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H274" s="16"/>
+      <c r="I274" s="16"/>
+      <c r="J274" s="16"/>
+      <c r="K274" s="16"/>
+      <c r="L274" s="16"/>
+      <c r="M274" s="16"/>
+      <c r="N274" s="16"/>
+      <c r="O274" s="16"/>
+      <c r="P274" s="16"/>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A275" s="15" t="s">
+        <v>973</v>
+      </c>
+      <c r="B275" s="15" t="s">
+        <v>974</v>
+      </c>
+      <c r="C275" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D275" s="15" t="s">
+        <v>975</v>
+      </c>
+      <c r="E275" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G275" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H275" s="16"/>
+      <c r="I275" s="16"/>
+      <c r="J275" s="16"/>
+      <c r="K275" s="16"/>
+      <c r="L275" s="16"/>
+      <c r="M275" s="16"/>
+      <c r="N275" s="16"/>
+      <c r="O275" s="16"/>
+      <c r="P275" s="16"/>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A276" s="15" t="s">
+        <v>976</v>
+      </c>
+      <c r="B276" s="15" t="s">
+        <v>977</v>
+      </c>
+      <c r="C276" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D276" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="E276" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G276" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H276" s="16"/>
+      <c r="I276" s="16"/>
+      <c r="J276" s="16"/>
+      <c r="K276" s="16"/>
+      <c r="L276" s="16"/>
+      <c r="M276" s="16"/>
+      <c r="N276" s="16"/>
+      <c r="O276" s="16"/>
+      <c r="P276" s="16"/>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A277" s="15" t="s">
+        <v>979</v>
+      </c>
+      <c r="B277" s="15" t="s">
+        <v>980</v>
+      </c>
+      <c r="C277" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D277" s="15" t="s">
+        <v>981</v>
+      </c>
+      <c r="E277" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G277" s="16" t="s">
+        <v>982</v>
+      </c>
+      <c r="H277" s="16"/>
+      <c r="I277" s="16"/>
+      <c r="J277" s="16"/>
+      <c r="K277" s="16"/>
+      <c r="L277" s="16"/>
+      <c r="M277" s="16"/>
+      <c r="N277" s="16"/>
+      <c r="O277" s="16"/>
+      <c r="P277" s="16"/>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A278" s="15" t="s">
+        <v>983</v>
+      </c>
+      <c r="B278" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="C278" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D278" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="E278" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G278" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H278" s="16"/>
+      <c r="I278" s="16"/>
+      <c r="J278" s="16"/>
+      <c r="K278" s="16"/>
+      <c r="L278" s="16"/>
+      <c r="M278" s="16"/>
+      <c r="N278" s="16"/>
+      <c r="O278" s="16"/>
+      <c r="P278" s="16"/>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A279" s="15" t="s">
+        <v>986</v>
+      </c>
+      <c r="B279" s="15" t="s">
+        <v>987</v>
+      </c>
+      <c r="C279" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D279" s="15" t="s">
+        <v>988</v>
+      </c>
+      <c r="E279" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G279" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H279" s="16"/>
+      <c r="I279" s="16"/>
+      <c r="J279" s="16"/>
+      <c r="K279" s="16"/>
+      <c r="L279" s="16"/>
+      <c r="M279" s="16"/>
+      <c r="N279" s="16"/>
+      <c r="O279" s="16"/>
+      <c r="P279" s="16"/>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A280" s="15" t="s">
+        <v>989</v>
+      </c>
+      <c r="B280" s="15" t="s">
+        <v>990</v>
+      </c>
+      <c r="C280" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D280" s="15" t="s">
+        <v>991</v>
+      </c>
+      <c r="E280" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G280" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H280" s="16"/>
+      <c r="I280" s="16"/>
+      <c r="J280" s="16"/>
+      <c r="K280" s="16"/>
+      <c r="L280" s="16"/>
+      <c r="M280" s="16"/>
+      <c r="N280" s="16"/>
+      <c r="O280" s="16"/>
+      <c r="P280" s="16"/>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A281" s="15" t="s">
+        <v>992</v>
+      </c>
+      <c r="B281" s="15" t="s">
+        <v>993</v>
+      </c>
+      <c r="C281" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D281" s="15" t="s">
+        <v>994</v>
+      </c>
+      <c r="E281" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G281" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H281" s="16"/>
+      <c r="I281" s="16"/>
+      <c r="J281" s="16"/>
+      <c r="K281" s="16"/>
+      <c r="L281" s="16"/>
+      <c r="M281" s="16"/>
+      <c r="N281" s="16"/>
+      <c r="O281" s="16"/>
+      <c r="P281" s="16"/>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A282" s="15" t="s">
+        <v>995</v>
+      </c>
+      <c r="B282" s="15" t="s">
+        <v>996</v>
+      </c>
+      <c r="C282" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D282" s="15" t="s">
+        <v>997</v>
+      </c>
+      <c r="E282" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G282" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H282" s="16"/>
+      <c r="I282" s="16"/>
+      <c r="J282" s="16"/>
+      <c r="K282" s="16"/>
+      <c r="L282" s="16"/>
+      <c r="M282" s="16"/>
+      <c r="N282" s="16"/>
+      <c r="O282" s="16"/>
+      <c r="P282" s="16"/>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A283" s="15" t="s">
+        <v>998</v>
+      </c>
+      <c r="B283" s="15" t="s">
+        <v>999</v>
+      </c>
+      <c r="C283" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D283" s="15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E283" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G283" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H283" s="16"/>
+      <c r="I283" s="16"/>
+      <c r="J283" s="16"/>
+      <c r="K283" s="16"/>
+      <c r="L283" s="16"/>
+      <c r="M283" s="16"/>
+      <c r="N283" s="16"/>
+      <c r="O283" s="16"/>
+      <c r="P283" s="16"/>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A284" s="15" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B284" s="15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C284" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D284" s="15" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E284" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G284" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H284" s="16"/>
+      <c r="I284" s="16"/>
+      <c r="J284" s="16"/>
+      <c r="K284" s="16"/>
+      <c r="L284" s="16"/>
+      <c r="M284" s="16"/>
+      <c r="N284" s="16"/>
+      <c r="O284" s="16"/>
+      <c r="P284" s="16"/>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A285" s="15" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B285" s="15" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C285" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D285" s="15" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E285" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G285" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H285" s="16"/>
+      <c r="I285" s="16"/>
+      <c r="J285" s="16"/>
+      <c r="K285" s="16"/>
+      <c r="L285" s="16"/>
+      <c r="M285" s="16"/>
+      <c r="N285" s="16"/>
+      <c r="O285" s="16"/>
+      <c r="P285" s="16"/>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A286" s="17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B286" s="15" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C286" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D286" s="15" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E286" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G286" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H286" s="16"/>
+      <c r="I286" s="16"/>
+      <c r="J286" s="16"/>
+      <c r="K286" s="16"/>
+      <c r="L286" s="16"/>
+      <c r="M286" s="16"/>
+      <c r="N286" s="16"/>
+      <c r="O286" s="16"/>
+      <c r="P286" s="16"/>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A287" s="18" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B287" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C287" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D287" s="15" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E287" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G287" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H287" s="16"/>
+      <c r="I287" s="16"/>
+      <c r="J287" s="16"/>
+      <c r="K287" s="16"/>
+      <c r="L287" s="16"/>
+      <c r="M287" s="16"/>
+      <c r="N287" s="16"/>
+      <c r="O287" s="16"/>
+      <c r="P287" s="16"/>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A288" s="18" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B288" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C288" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D288" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E288" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G288" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H288" s="16"/>
+      <c r="I288" s="16"/>
+      <c r="J288" s="16"/>
+      <c r="K288" s="16"/>
+      <c r="L288" s="16"/>
+      <c r="M288" s="16"/>
+      <c r="N288" s="16"/>
+      <c r="O288" s="16"/>
+      <c r="P288" s="16"/>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A289" s="15" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B289" s="15" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C289" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D289" s="15" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E289" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G289" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H289" s="16"/>
+      <c r="I289" s="16"/>
+      <c r="J289" s="16"/>
+      <c r="K289" s="16"/>
+      <c r="L289" s="16"/>
+      <c r="M289" s="16"/>
+      <c r="N289" s="16"/>
+      <c r="O289" s="16"/>
+      <c r="P289" s="16"/>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A290" s="15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B290" s="15" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C290" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D290" s="15" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E290" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G290" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H290" s="16"/>
+      <c r="I290" s="16"/>
+      <c r="J290" s="16"/>
+      <c r="K290" s="16"/>
+      <c r="L290" s="16"/>
+      <c r="M290" s="16"/>
+      <c r="N290" s="16"/>
+      <c r="O290" s="16"/>
+      <c r="P290" s="16"/>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A291" s="15" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C291" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D291" s="15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E291" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G291" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H291" s="16"/>
+      <c r="I291" s="16"/>
+      <c r="J291" s="16"/>
+      <c r="K291" s="16"/>
+      <c r="L291" s="16"/>
+      <c r="M291" s="16"/>
+      <c r="N291" s="16"/>
+      <c r="O291" s="16"/>
+      <c r="P291" s="16"/>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A292" s="15" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B292" s="15" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C292" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D292" s="15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E292" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G292" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H292" s="16"/>
+      <c r="I292" s="16"/>
+      <c r="J292" s="16"/>
+      <c r="K292" s="16"/>
+      <c r="L292" s="16"/>
+      <c r="M292" s="16"/>
+      <c r="N292" s="16"/>
+      <c r="O292" s="16"/>
+      <c r="P292" s="16"/>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A293" s="15" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B293" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C293" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D293" s="15" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E293" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G293" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H293" s="16"/>
+      <c r="I293" s="16"/>
+      <c r="J293" s="16"/>
+      <c r="K293" s="16"/>
+      <c r="L293" s="16"/>
+      <c r="M293" s="16"/>
+      <c r="N293" s="16"/>
+      <c r="O293" s="16"/>
+      <c r="P293" s="16"/>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A294" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B294" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C294" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="D294" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E294" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G294" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H294" s="16"/>
+      <c r="I294" s="16"/>
+      <c r="J294" s="16"/>
+      <c r="K294" s="16"/>
+      <c r="L294" s="16"/>
+      <c r="M294" s="16"/>
+      <c r="N294" s="16"/>
+      <c r="O294" s="16"/>
+      <c r="P294" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P223" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
